--- a/research/traditional_assets/database/data/mexico/mexico_retail_building_supply.xlsx
+++ b/research/traditional_assets/database/data/mexico/mexico_retail_building_supply.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1112925721327847</v>
+        <v>0.1109901944163863</v>
       </c>
       <c r="C2">
-        <v>647.378323261736</v>
+        <v>642.557326461288</v>
       </c>
       <c r="D2">
-        <v>631.178323261736</v>
+        <v>633.2073264612879</v>
       </c>
       <c r="E2">
-        <v>-268.6</v>
+        <v>-261.75</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>6.850000000000001</v>
       </c>
       <c r="G2">
         <v>16.2</v>
@@ -1451,28 +1451,28 @@
         <v>130.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.344555</v>
       </c>
       <c r="N2">
-        <v>130.6</v>
+        <v>130.255445</v>
       </c>
       <c r="O2">
-        <v>39.18</v>
+        <v>39.07663349999999</v>
       </c>
       <c r="P2">
-        <v>91.41999999999999</v>
+        <v>91.17881149999999</v>
       </c>
       <c r="Q2">
-        <v>103.32</v>
+        <v>103.0788115</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1112925721327847</v>
+        <v>0.1117556509256427</v>
       </c>
       <c r="T2">
-        <v>0.9529967248041119</v>
+        <v>0.959735085484545</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>379.0396308281696</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1109901944163863</v>
+        <v>0.110687816699988</v>
       </c>
       <c r="C3">
-        <v>642.557326461288</v>
+        <v>637.7494167098203</v>
       </c>
       <c r="D3">
-        <v>633.2073264612879</v>
+        <v>635.2494167098203</v>
       </c>
       <c r="E3">
-        <v>-261.75</v>
+        <v>-254.9</v>
       </c>
       <c r="F3">
-        <v>6.850000000000001</v>
+        <v>13.7</v>
       </c>
       <c r="G3">
         <v>16.2</v>
@@ -1533,28 +1533,28 @@
         <v>130.6</v>
       </c>
       <c r="M3">
-        <v>0.344555</v>
+        <v>0.68911</v>
       </c>
       <c r="N3">
-        <v>130.255445</v>
+        <v>129.91089</v>
       </c>
       <c r="O3">
-        <v>39.07663349999999</v>
+        <v>38.973267</v>
       </c>
       <c r="P3">
-        <v>91.17881149999999</v>
+        <v>90.937623</v>
       </c>
       <c r="Q3">
-        <v>103.0788115</v>
+        <v>102.837623</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1117556509256427</v>
+        <v>0.1122281803061101</v>
       </c>
       <c r="T3">
-        <v>0.959735085484545</v>
+        <v>0.9666109637298849</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>379.0396308281696</v>
+        <v>189.5198154140848</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.110687816699988</v>
+        <v>0.1103854389835896</v>
       </c>
       <c r="C4">
-        <v>637.7494167098203</v>
+        <v>632.9547210339828</v>
       </c>
       <c r="D4">
-        <v>635.2494167098203</v>
+        <v>637.3047210339827</v>
       </c>
       <c r="E4">
-        <v>-254.9</v>
+        <v>-248.05</v>
       </c>
       <c r="F4">
-        <v>13.7</v>
+        <v>20.55</v>
       </c>
       <c r="G4">
         <v>16.2</v>
@@ -1615,28 +1615,28 @@
         <v>130.6</v>
       </c>
       <c r="M4">
-        <v>0.68911</v>
+        <v>1.033665</v>
       </c>
       <c r="N4">
-        <v>129.91089</v>
+        <v>129.566335</v>
       </c>
       <c r="O4">
-        <v>38.973267</v>
+        <v>38.86990049999999</v>
       </c>
       <c r="P4">
-        <v>90.937623</v>
+        <v>90.69643449999998</v>
       </c>
       <c r="Q4">
-        <v>102.837623</v>
+        <v>102.5964345</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1122281803061101</v>
+        <v>0.1127104525604016</v>
       </c>
       <c r="T4">
-        <v>0.9666109637298849</v>
+        <v>0.9736286126606957</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>189.5198154140848</v>
+        <v>126.3465436093899</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1103854389835896</v>
+        <v>0.1100830612671912</v>
       </c>
       <c r="C5">
-        <v>632.9547210339828</v>
+        <v>628.1733681097035</v>
       </c>
       <c r="D5">
-        <v>637.3047210339827</v>
+        <v>639.3733681097034</v>
       </c>
       <c r="E5">
-        <v>-248.05</v>
+        <v>-241.2</v>
       </c>
       <c r="F5">
-        <v>20.55</v>
+        <v>27.4</v>
       </c>
       <c r="G5">
         <v>16.2</v>
@@ -1697,28 +1697,28 @@
         <v>130.6</v>
       </c>
       <c r="M5">
-        <v>1.033665</v>
+        <v>1.37822</v>
       </c>
       <c r="N5">
-        <v>129.566335</v>
+        <v>129.22178</v>
       </c>
       <c r="O5">
-        <v>38.86990049999999</v>
+        <v>38.766534</v>
       </c>
       <c r="P5">
-        <v>90.69643449999998</v>
+        <v>90.45524599999999</v>
       </c>
       <c r="Q5">
-        <v>102.5964345</v>
+        <v>102.355246</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1127104525604016</v>
+        <v>0.1132027721533242</v>
       </c>
       <c r="T5">
-        <v>0.9736286126606957</v>
+        <v>0.9807924626108984</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>126.3465436093899</v>
+        <v>94.75990770704242</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1100830612671912</v>
+        <v>0.1097806835507929</v>
       </c>
       <c r="C6">
-        <v>628.1733681097035</v>
+        <v>623.4054882890445</v>
       </c>
       <c r="D6">
-        <v>639.3733681097034</v>
+        <v>641.4554882890444</v>
       </c>
       <c r="E6">
-        <v>-241.2</v>
+        <v>-234.35</v>
       </c>
       <c r="F6">
-        <v>27.4</v>
+        <v>34.25</v>
       </c>
       <c r="G6">
         <v>16.2</v>
@@ -1779,28 +1779,28 @@
         <v>130.6</v>
       </c>
       <c r="M6">
-        <v>1.37822</v>
+        <v>1.722775</v>
       </c>
       <c r="N6">
-        <v>129.22178</v>
+        <v>128.877225</v>
       </c>
       <c r="O6">
-        <v>38.766534</v>
+        <v>38.66316749999999</v>
       </c>
       <c r="P6">
-        <v>90.45524599999999</v>
+        <v>90.2140575</v>
       </c>
       <c r="Q6">
-        <v>102.355246</v>
+        <v>102.1140575</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1132027721533242</v>
+        <v>0.1137054563692557</v>
       </c>
       <c r="T6">
-        <v>0.9807924626108984</v>
+        <v>0.9881071304547896</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>94.75990770704242</v>
+        <v>75.80792616563393</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1097806835507929</v>
+        <v>0.1094783058343945</v>
       </c>
       <c r="C7">
-        <v>623.4054882890445</v>
+        <v>618.6512136275817</v>
       </c>
       <c r="D7">
-        <v>641.4554882890444</v>
+        <v>643.5512136275817</v>
       </c>
       <c r="E7">
-        <v>-234.35</v>
+        <v>-227.5</v>
       </c>
       <c r="F7">
-        <v>34.25</v>
+        <v>41.1</v>
       </c>
       <c r="G7">
         <v>16.2</v>
@@ -1861,28 +1861,28 @@
         <v>130.6</v>
       </c>
       <c r="M7">
-        <v>1.722775</v>
+        <v>2.06733</v>
       </c>
       <c r="N7">
-        <v>128.877225</v>
+        <v>128.53267</v>
       </c>
       <c r="O7">
-        <v>38.66316749999999</v>
+        <v>38.559801</v>
       </c>
       <c r="P7">
-        <v>90.2140575</v>
+        <v>89.972869</v>
       </c>
       <c r="Q7">
-        <v>102.1140575</v>
+        <v>101.872869</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1137054563692557</v>
+        <v>0.1142188359940367</v>
       </c>
       <c r="T7">
-        <v>0.9881071304547896</v>
+        <v>0.9955774295294019</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>75.80792616563393</v>
+        <v>63.17327180469494</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1094783058343945</v>
+        <v>0.1091759281179962</v>
       </c>
       <c r="C8">
-        <v>618.6512136275817</v>
+        <v>613.9106779123243</v>
       </c>
       <c r="D8">
-        <v>643.5512136275817</v>
+        <v>645.6606779123243</v>
       </c>
       <c r="E8">
-        <v>-227.5</v>
+        <v>-220.65</v>
       </c>
       <c r="F8">
-        <v>41.1</v>
+        <v>47.95</v>
       </c>
       <c r="G8">
         <v>16.2</v>
@@ -1943,28 +1943,28 @@
         <v>130.6</v>
       </c>
       <c r="M8">
-        <v>2.06733</v>
+        <v>2.411885</v>
       </c>
       <c r="N8">
-        <v>128.53267</v>
+        <v>128.188115</v>
       </c>
       <c r="O8">
-        <v>38.559801</v>
+        <v>38.45643449999999</v>
       </c>
       <c r="P8">
-        <v>89.972869</v>
+        <v>89.73168049999998</v>
       </c>
       <c r="Q8">
-        <v>101.872869</v>
+        <v>101.6316805</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1142188359940367</v>
+        <v>0.1147432560408561</v>
       </c>
       <c r="T8">
-        <v>0.9955774295294019</v>
+        <v>1.003208380197017</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>63.17327180469494</v>
+        <v>54.14851868973852</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1091759281179962</v>
+        <v>0.1088735504015978</v>
       </c>
       <c r="C9">
-        <v>613.9106779123243</v>
+        <v>609.1840166901857</v>
       </c>
       <c r="D9">
-        <v>645.6606779123243</v>
+        <v>647.7840166901856</v>
       </c>
       <c r="E9">
-        <v>-220.65</v>
+        <v>-213.8</v>
       </c>
       <c r="F9">
-        <v>47.95</v>
+        <v>54.8</v>
       </c>
       <c r="G9">
         <v>16.2</v>
@@ -2025,28 +2025,28 @@
         <v>130.6</v>
       </c>
       <c r="M9">
-        <v>2.411885</v>
+        <v>2.75644</v>
       </c>
       <c r="N9">
-        <v>128.188115</v>
+        <v>127.84356</v>
       </c>
       <c r="O9">
-        <v>38.45643449999999</v>
+        <v>38.353068</v>
       </c>
       <c r="P9">
-        <v>89.73168049999998</v>
+        <v>89.49049199999999</v>
       </c>
       <c r="Q9">
-        <v>101.6316805</v>
+        <v>101.390492</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1147432560408561</v>
+        <v>0.1152790765234759</v>
       </c>
       <c r="T9">
-        <v>1.003208380197017</v>
+        <v>1.011005221096536</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>54.14851868973852</v>
+        <v>47.37995385352121</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1088735504015978</v>
+        <v>0.1085711726851995</v>
       </c>
       <c r="C10">
-        <v>609.1840166901857</v>
+        <v>604.4713672970159</v>
       </c>
       <c r="D10">
-        <v>647.7840166901856</v>
+        <v>649.9213672970159</v>
       </c>
       <c r="E10">
-        <v>-213.8</v>
+        <v>-206.95</v>
       </c>
       <c r="F10">
-        <v>54.8</v>
+        <v>61.65</v>
       </c>
       <c r="G10">
         <v>16.2</v>
@@ -2107,28 +2107,28 @@
         <v>130.6</v>
       </c>
       <c r="M10">
-        <v>2.75644</v>
+        <v>3.100995</v>
       </c>
       <c r="N10">
-        <v>127.84356</v>
+        <v>127.499005</v>
       </c>
       <c r="O10">
-        <v>38.353068</v>
+        <v>38.2497015</v>
       </c>
       <c r="P10">
-        <v>89.49049199999999</v>
+        <v>89.2493035</v>
       </c>
       <c r="Q10">
-        <v>101.390492</v>
+        <v>101.1493035</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1152790765234759</v>
+        <v>0.115826673280439</v>
       </c>
       <c r="T10">
-        <v>1.011005221096536</v>
+        <v>1.018973421136704</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>47.37995385352121</v>
+        <v>42.1155145364633</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1085711726851995</v>
+        <v>0.1082687949688011</v>
       </c>
       <c r="C11">
-        <v>604.4713672970159</v>
+        <v>599.7728688872139</v>
       </c>
       <c r="D11">
-        <v>649.9213672970159</v>
+        <v>652.0728688872139</v>
       </c>
       <c r="E11">
-        <v>-206.95</v>
+        <v>-200.1</v>
       </c>
       <c r="F11">
-        <v>61.65</v>
+        <v>68.5</v>
       </c>
       <c r="G11">
         <v>16.2</v>
@@ -2189,28 +2189,28 @@
         <v>130.6</v>
       </c>
       <c r="M11">
-        <v>3.100995</v>
+        <v>3.44555</v>
       </c>
       <c r="N11">
-        <v>127.499005</v>
+        <v>127.15445</v>
       </c>
       <c r="O11">
-        <v>38.2497015</v>
+        <v>38.146335</v>
       </c>
       <c r="P11">
-        <v>89.2493035</v>
+        <v>89.008115</v>
       </c>
       <c r="Q11">
-        <v>101.1493035</v>
+        <v>100.908115</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.115826673280439</v>
+        <v>0.1163864388542235</v>
       </c>
       <c r="T11">
-        <v>1.018973421136704</v>
+        <v>1.027118692288876</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>42.1155145364633</v>
+        <v>37.90396308281696</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1082687949688011</v>
+        <v>0.1079664172524028</v>
       </c>
       <c r="C12">
-        <v>599.7728688872139</v>
+        <v>595.0886624639263</v>
       </c>
       <c r="D12">
-        <v>652.0728688872139</v>
+        <v>654.2386624639263</v>
       </c>
       <c r="E12">
-        <v>-200.1</v>
+        <v>-193.25</v>
       </c>
       <c r="F12">
-        <v>68.5</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="G12">
         <v>16.2</v>
@@ -2271,28 +2271,28 @@
         <v>130.6</v>
       </c>
       <c r="M12">
-        <v>3.44555</v>
+        <v>3.790105</v>
       </c>
       <c r="N12">
-        <v>127.15445</v>
+        <v>126.809895</v>
       </c>
       <c r="O12">
-        <v>38.146335</v>
+        <v>38.0429685</v>
       </c>
       <c r="P12">
-        <v>89.008115</v>
+        <v>88.7669265</v>
       </c>
       <c r="Q12">
-        <v>100.908115</v>
+        <v>100.6669265</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1163864388542235</v>
+        <v>0.116958783429666</v>
       </c>
       <c r="T12">
-        <v>1.027118692288876</v>
+        <v>1.03544700324222</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>37.90396308281696</v>
+        <v>34.45814825710634</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1079664172524028</v>
+        <v>0.1076640395360044</v>
       </c>
       <c r="C13">
-        <v>595.0886624639263</v>
+        <v>590.4188909098536</v>
       </c>
       <c r="D13">
-        <v>654.2386624639263</v>
+        <v>656.4188909098536</v>
       </c>
       <c r="E13">
-        <v>-193.25</v>
+        <v>-186.4</v>
       </c>
       <c r="F13">
-        <v>75.34999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="G13">
         <v>16.2</v>
@@ -2353,28 +2353,28 @@
         <v>130.6</v>
       </c>
       <c r="M13">
-        <v>3.790105</v>
+        <v>4.13466</v>
       </c>
       <c r="N13">
-        <v>126.809895</v>
+        <v>126.46534</v>
       </c>
       <c r="O13">
-        <v>38.0429685</v>
+        <v>37.939602</v>
       </c>
       <c r="P13">
-        <v>88.7669265</v>
+        <v>88.52573799999999</v>
       </c>
       <c r="Q13">
-        <v>100.6669265</v>
+        <v>100.425738</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.116958783429666</v>
+        <v>0.1175441358363687</v>
       </c>
       <c r="T13">
-        <v>1.03544700324222</v>
+        <v>1.043964593989959</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>34.45814825710634</v>
+        <v>31.58663590234747</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1076640395360044</v>
+        <v>0.107361661819606</v>
       </c>
       <c r="C14">
-        <v>590.4188909098536</v>
+        <v>585.7636990186716</v>
       </c>
       <c r="D14">
-        <v>656.4188909098536</v>
+        <v>658.6136990186715</v>
       </c>
       <c r="E14">
-        <v>-186.4</v>
+        <v>-179.55</v>
       </c>
       <c r="F14">
-        <v>82.2</v>
+        <v>89.05</v>
       </c>
       <c r="G14">
         <v>16.2</v>
@@ -2435,28 +2435,28 @@
         <v>130.6</v>
       </c>
       <c r="M14">
-        <v>4.13466</v>
+        <v>4.479215</v>
       </c>
       <c r="N14">
-        <v>126.46534</v>
+        <v>126.120785</v>
       </c>
       <c r="O14">
-        <v>37.939602</v>
+        <v>37.8362355</v>
       </c>
       <c r="P14">
-        <v>88.52573799999999</v>
+        <v>88.2845495</v>
       </c>
       <c r="Q14">
-        <v>100.425738</v>
+        <v>100.1845495</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1175441358363687</v>
+        <v>0.1181429446202368</v>
       </c>
       <c r="T14">
-        <v>1.043964593989959</v>
+        <v>1.052677991421553</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>31.58663590234747</v>
+        <v>29.15689467908997</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.107361661819606</v>
+        <v>0.1070592841032077</v>
       </c>
       <c r="C15">
-        <v>585.7636990186716</v>
+        <v>581.1232335270859</v>
       </c>
       <c r="D15">
-        <v>658.6136990186715</v>
+        <v>660.8232335270858</v>
       </c>
       <c r="E15">
-        <v>-179.55</v>
+        <v>-172.7</v>
       </c>
       <c r="F15">
-        <v>89.05</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="G15">
         <v>16.2</v>
@@ -2517,28 +2517,28 @@
         <v>130.6</v>
       </c>
       <c r="M15">
-        <v>4.479215</v>
+        <v>4.82377</v>
       </c>
       <c r="N15">
-        <v>126.120785</v>
+        <v>125.77623</v>
       </c>
       <c r="O15">
-        <v>37.8362355</v>
+        <v>37.732869</v>
       </c>
       <c r="P15">
-        <v>88.2845495</v>
+        <v>88.043361</v>
       </c>
       <c r="Q15">
-        <v>100.1845495</v>
+        <v>99.94336100000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1181429446202368</v>
+        <v>0.1187556791897764</v>
       </c>
       <c r="T15">
-        <v>1.052677991421553</v>
+        <v>1.06159402600272</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>29.15689467908997</v>
+        <v>27.07425934486926</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1070592841032077</v>
+        <v>0.1067569063868094</v>
       </c>
       <c r="C16">
-        <v>581.1232335270859</v>
+        <v>576.4976431475357</v>
       </c>
       <c r="D16">
-        <v>660.8232335270858</v>
+        <v>663.0476431475356</v>
       </c>
       <c r="E16">
-        <v>-172.7</v>
+        <v>-165.85</v>
       </c>
       <c r="F16">
-        <v>95.90000000000001</v>
+        <v>102.75</v>
       </c>
       <c r="G16">
         <v>16.2</v>
@@ -2599,28 +2599,28 @@
         <v>130.6</v>
       </c>
       <c r="M16">
-        <v>4.82377</v>
+        <v>5.168325</v>
       </c>
       <c r="N16">
-        <v>125.77623</v>
+        <v>125.431675</v>
       </c>
       <c r="O16">
-        <v>37.732869</v>
+        <v>37.6295025</v>
       </c>
       <c r="P16">
-        <v>88.043361</v>
+        <v>87.8021725</v>
       </c>
       <c r="Q16">
-        <v>99.94336100000001</v>
+        <v>99.7021725</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1187556791897764</v>
+        <v>0.1193828310433051</v>
       </c>
       <c r="T16">
-        <v>1.06159402600272</v>
+        <v>1.070719849632855</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>27.07425934486926</v>
+        <v>25.26930872187798</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1067569063868094</v>
+        <v>0.106454528670411</v>
       </c>
       <c r="C17">
-        <v>576.4976431475357</v>
+        <v>571.8870786015583</v>
       </c>
       <c r="D17">
-        <v>663.0476431475356</v>
+        <v>665.2870786015583</v>
       </c>
       <c r="E17">
-        <v>-165.85</v>
+        <v>-159</v>
       </c>
       <c r="F17">
-        <v>102.75</v>
+        <v>109.6</v>
       </c>
       <c r="G17">
         <v>16.2</v>
@@ -2681,28 +2681,28 @@
         <v>130.6</v>
       </c>
       <c r="M17">
-        <v>5.168324999999999</v>
+        <v>5.51288</v>
       </c>
       <c r="N17">
-        <v>125.431675</v>
+        <v>125.08712</v>
       </c>
       <c r="O17">
-        <v>37.6295025</v>
+        <v>37.526136</v>
       </c>
       <c r="P17">
-        <v>87.8021725</v>
+        <v>87.56098399999999</v>
       </c>
       <c r="Q17">
-        <v>99.7021725</v>
+        <v>99.460984</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1193828310433051</v>
+        <v>0.1200249150838226</v>
       </c>
       <c r="T17">
-        <v>1.070719849632855</v>
+        <v>1.080062954777993</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>25.26930872187798</v>
+        <v>23.6899769267606</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.106454528670411</v>
+        <v>0.1061521509540126</v>
       </c>
       <c r="C18">
-        <v>571.8870786015583</v>
+        <v>567.2916926538318</v>
       </c>
       <c r="D18">
-        <v>665.2870786015583</v>
+        <v>667.5416926538318</v>
       </c>
       <c r="E18">
-        <v>-159</v>
+        <v>-152.15</v>
       </c>
       <c r="F18">
-        <v>109.6</v>
+        <v>116.45</v>
       </c>
       <c r="G18">
         <v>16.2</v>
@@ -2763,28 +2763,28 @@
         <v>130.6</v>
       </c>
       <c r="M18">
-        <v>5.51288</v>
+        <v>5.857435</v>
       </c>
       <c r="N18">
-        <v>125.08712</v>
+        <v>124.742565</v>
       </c>
       <c r="O18">
-        <v>37.526136</v>
+        <v>37.4227695</v>
       </c>
       <c r="P18">
-        <v>87.56098399999999</v>
+        <v>87.3197955</v>
       </c>
       <c r="Q18">
-        <v>99.460984</v>
+        <v>99.2197955</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1200249150838226</v>
+        <v>0.1206824710289309</v>
       </c>
       <c r="T18">
-        <v>1.080062954777993</v>
+        <v>1.08963119498687</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>23.6899769267606</v>
+        <v>22.29644887224527</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1061521509540126</v>
+        <v>0.1058497732376143</v>
       </c>
       <c r="C19">
-        <v>567.2916926538318</v>
+        <v>562.7116401469139</v>
       </c>
       <c r="D19">
-        <v>667.5416926538318</v>
+        <v>669.8116401469138</v>
       </c>
       <c r="E19">
-        <v>-152.15</v>
+        <v>-145.3</v>
       </c>
       <c r="F19">
-        <v>116.45</v>
+        <v>123.3</v>
       </c>
       <c r="G19">
         <v>16.2</v>
@@ -2845,28 +2845,28 @@
         <v>130.6</v>
       </c>
       <c r="M19">
-        <v>5.857435</v>
+        <v>6.20199</v>
       </c>
       <c r="N19">
-        <v>124.742565</v>
+        <v>124.39801</v>
       </c>
       <c r="O19">
-        <v>37.4227695</v>
+        <v>37.319403</v>
       </c>
       <c r="P19">
-        <v>87.3197955</v>
+        <v>87.07860700000001</v>
       </c>
       <c r="Q19">
-        <v>99.2197955</v>
+        <v>98.97860700000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1206824710289309</v>
+        <v>0.1213560649239199</v>
       </c>
       <c r="T19">
-        <v>1.08963119498687</v>
+        <v>1.099432806908158</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>22.29644887224527</v>
+        <v>21.05775726823165</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1058497732376143</v>
+        <v>0.1055473955212159</v>
       </c>
       <c r="C20">
-        <v>562.7116401469137</v>
+        <v>558.1470780366911</v>
       </c>
       <c r="D20">
-        <v>669.8116401469136</v>
+        <v>672.0970780366911</v>
       </c>
       <c r="E20">
-        <v>-145.3</v>
+        <v>-138.45</v>
       </c>
       <c r="F20">
-        <v>123.3</v>
+        <v>130.15</v>
       </c>
       <c r="G20">
         <v>16.2</v>
@@ -2927,28 +2927,28 @@
         <v>130.6</v>
       </c>
       <c r="M20">
-        <v>6.201989999999999</v>
+        <v>6.546545</v>
       </c>
       <c r="N20">
-        <v>124.39801</v>
+        <v>124.053455</v>
       </c>
       <c r="O20">
-        <v>37.319403</v>
+        <v>37.2160365</v>
       </c>
       <c r="P20">
-        <v>87.07860700000001</v>
+        <v>86.8374185</v>
       </c>
       <c r="Q20">
-        <v>98.97860700000001</v>
+        <v>98.7374185</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1213560649239199</v>
+        <v>0.1220462907669332</v>
       </c>
       <c r="T20">
-        <v>1.099432806908158</v>
+        <v>1.109476433938614</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>21.05775726823165</v>
+        <v>19.94945425411419</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1055473955212159</v>
+        <v>0.1052450178048176</v>
       </c>
       <c r="C21">
-        <v>558.1470780366911</v>
+        <v>553.5981654285567</v>
       </c>
       <c r="D21">
-        <v>672.0970780366911</v>
+        <v>674.3981654285567</v>
       </c>
       <c r="E21">
-        <v>-138.45</v>
+        <v>-131.6</v>
       </c>
       <c r="F21">
-        <v>130.15</v>
+        <v>137</v>
       </c>
       <c r="G21">
         <v>16.2</v>
@@ -3009,28 +3009,28 @@
         <v>130.6</v>
       </c>
       <c r="M21">
-        <v>6.546545</v>
+        <v>6.8911</v>
       </c>
       <c r="N21">
-        <v>124.053455</v>
+        <v>123.7089</v>
       </c>
       <c r="O21">
-        <v>37.2160365</v>
+        <v>37.11267</v>
       </c>
       <c r="P21">
-        <v>86.8374185</v>
+        <v>86.59622999999999</v>
       </c>
       <c r="Q21">
-        <v>98.7374185</v>
+        <v>98.49623</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1220462907669332</v>
+        <v>0.122753772256022</v>
       </c>
       <c r="T21">
-        <v>1.109476433938614</v>
+        <v>1.119771151644831</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>19.94945425411419</v>
+        <v>18.95198154140848</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1052450178048176</v>
+        <v>0.1049426400884192</v>
       </c>
       <c r="C22">
-        <v>553.5981654285567</v>
+        <v>549.0650636143322</v>
       </c>
       <c r="D22">
-        <v>674.3981654285567</v>
+        <v>676.7150636143322</v>
       </c>
       <c r="E22">
-        <v>-131.6</v>
+        <v>-124.75</v>
       </c>
       <c r="F22">
-        <v>137</v>
+        <v>143.85</v>
       </c>
       <c r="G22">
         <v>16.2</v>
@@ -3091,28 +3091,28 @@
         <v>130.6</v>
       </c>
       <c r="M22">
-        <v>6.8911</v>
+        <v>7.235655</v>
       </c>
       <c r="N22">
-        <v>123.7089</v>
+        <v>123.364345</v>
       </c>
       <c r="O22">
-        <v>37.11267</v>
+        <v>37.0093035</v>
       </c>
       <c r="P22">
-        <v>86.59622999999999</v>
+        <v>86.3550415</v>
       </c>
       <c r="Q22">
-        <v>98.49623</v>
+        <v>98.2550415</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.122753772256022</v>
+        <v>0.1234791646688851</v>
       </c>
       <c r="T22">
-        <v>1.119771151644831</v>
+        <v>1.130326495115763</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>18.95198154140848</v>
+        <v>18.04950622991284</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1049426400884192</v>
+        <v>0.1046402623720209</v>
       </c>
       <c r="C23">
-        <v>549.0650636143324</v>
+        <v>544.5479361099569</v>
       </c>
       <c r="D23">
-        <v>676.7150636143324</v>
+        <v>679.0479361099568</v>
       </c>
       <c r="E23">
-        <v>-124.75</v>
+        <v>-117.9</v>
       </c>
       <c r="F23">
-        <v>143.85</v>
+        <v>150.7</v>
       </c>
       <c r="G23">
         <v>16.2</v>
@@ -3173,28 +3173,28 @@
         <v>130.6</v>
       </c>
       <c r="M23">
-        <v>7.235655</v>
+        <v>7.580209999999999</v>
       </c>
       <c r="N23">
-        <v>123.364345</v>
+        <v>123.01979</v>
       </c>
       <c r="O23">
-        <v>37.0093035</v>
+        <v>36.905937</v>
       </c>
       <c r="P23">
-        <v>86.3550415</v>
+        <v>86.11385300000001</v>
       </c>
       <c r="Q23">
-        <v>98.2550415</v>
+        <v>98.01385300000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1234791646688851</v>
+        <v>0.1242231568872063</v>
       </c>
       <c r="T23">
-        <v>1.130326495115763</v>
+        <v>1.141152488419283</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>18.04950622991284</v>
+        <v>17.22907412855317</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1046402623720209</v>
+        <v>0.1043378846556225</v>
       </c>
       <c r="C24">
-        <v>544.5479361099569</v>
+        <v>540.0469486939539</v>
       </c>
       <c r="D24">
-        <v>679.0479361099568</v>
+        <v>681.396948693954</v>
       </c>
       <c r="E24">
-        <v>-117.9</v>
+        <v>-111.05</v>
       </c>
       <c r="F24">
-        <v>150.7</v>
+        <v>157.55</v>
       </c>
       <c r="G24">
         <v>16.2</v>
@@ -3255,28 +3255,28 @@
         <v>130.6</v>
       </c>
       <c r="M24">
-        <v>7.580209999999999</v>
+        <v>7.924765</v>
       </c>
       <c r="N24">
-        <v>123.01979</v>
+        <v>122.675235</v>
       </c>
       <c r="O24">
-        <v>36.905937</v>
+        <v>36.8025705</v>
       </c>
       <c r="P24">
-        <v>86.11385300000001</v>
+        <v>85.8726645</v>
       </c>
       <c r="Q24">
-        <v>98.01385300000001</v>
+        <v>97.7726645</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1242231568872063</v>
+        <v>0.1249864735787306</v>
       </c>
       <c r="T24">
-        <v>1.141152488419283</v>
+        <v>1.152259676354062</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>17.22907412855317</v>
+        <v>16.47998394905085</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1043378846556225</v>
+        <v>0.1040355069392242</v>
       </c>
       <c r="C25">
-        <v>540.0469486939539</v>
+        <v>535.562269446704</v>
       </c>
       <c r="D25">
-        <v>681.396948693954</v>
+        <v>683.762269446704</v>
       </c>
       <c r="E25">
-        <v>-111.05</v>
+        <v>-104.2</v>
       </c>
       <c r="F25">
-        <v>157.55</v>
+        <v>164.4</v>
       </c>
       <c r="G25">
         <v>16.2</v>
@@ -3337,28 +3337,28 @@
         <v>130.6</v>
       </c>
       <c r="M25">
-        <v>7.924765</v>
+        <v>8.26932</v>
       </c>
       <c r="N25">
-        <v>122.675235</v>
+        <v>122.33068</v>
       </c>
       <c r="O25">
-        <v>36.8025705</v>
+        <v>36.699204</v>
       </c>
       <c r="P25">
-        <v>85.8726645</v>
+        <v>85.63147599999999</v>
       </c>
       <c r="Q25">
-        <v>97.7726645</v>
+        <v>97.531476</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1249864735787306</v>
+        <v>0.1257698775516108</v>
       </c>
       <c r="T25">
-        <v>1.152259676354062</v>
+        <v>1.163659158708179</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>16.47998394905085</v>
+        <v>15.79331795117374</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1040355069392242</v>
+        <v>0.1037331292228258</v>
       </c>
       <c r="C26">
-        <v>535.562269446704</v>
+        <v>531.0940687905332</v>
       </c>
       <c r="D26">
-        <v>683.762269446704</v>
+        <v>686.1440687905332</v>
       </c>
       <c r="E26">
-        <v>-104.2</v>
+        <v>-97.35000000000002</v>
       </c>
       <c r="F26">
-        <v>164.4</v>
+        <v>171.25</v>
       </c>
       <c r="G26">
         <v>16.2</v>
@@ -3419,28 +3419,28 @@
         <v>130.6</v>
       </c>
       <c r="M26">
-        <v>8.26932</v>
+        <v>8.613875</v>
       </c>
       <c r="N26">
-        <v>122.33068</v>
+        <v>121.986125</v>
       </c>
       <c r="O26">
-        <v>36.699204</v>
+        <v>36.59583749999999</v>
       </c>
       <c r="P26">
-        <v>85.63147599999999</v>
+        <v>85.3902875</v>
       </c>
       <c r="Q26">
-        <v>97.531476</v>
+        <v>97.29028750000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1257698775516108</v>
+        <v>0.1265741722971011</v>
       </c>
       <c r="T26">
-        <v>1.163659158708179</v>
+        <v>1.175362627258405</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>15.79331795117374</v>
+        <v>15.16158523312678</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1037331292228258</v>
+        <v>0.1034307515064275</v>
       </c>
       <c r="C27">
-        <v>531.0940687905332</v>
+        <v>526.6425195306474</v>
       </c>
       <c r="D27">
-        <v>686.1440687905332</v>
+        <v>688.5425195306474</v>
       </c>
       <c r="E27">
-        <v>-97.35000000000002</v>
+        <v>-90.50000000000003</v>
       </c>
       <c r="F27">
-        <v>171.25</v>
+        <v>178.1</v>
       </c>
       <c r="G27">
         <v>16.2</v>
@@ -3501,28 +3501,28 @@
         <v>130.6</v>
       </c>
       <c r="M27">
-        <v>8.613875</v>
+        <v>8.95843</v>
       </c>
       <c r="N27">
-        <v>121.986125</v>
+        <v>121.64157</v>
       </c>
       <c r="O27">
-        <v>36.59583749999999</v>
+        <v>36.492471</v>
       </c>
       <c r="P27">
-        <v>85.3902875</v>
+        <v>85.14909900000001</v>
       </c>
       <c r="Q27">
-        <v>97.29028750000001</v>
+        <v>97.04909900000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1265741722971011</v>
+        <v>0.1274002047384155</v>
       </c>
       <c r="T27">
-        <v>1.175362627258405</v>
+        <v>1.187382405769448</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>15.16158523312678</v>
+        <v>14.57844733954499</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1034307515064275</v>
+        <v>0.1031283737900291</v>
       </c>
       <c r="C28">
-        <v>526.6425195306474</v>
+        <v>522.2077968969244</v>
       </c>
       <c r="D28">
-        <v>688.5425195306474</v>
+        <v>690.9577968969244</v>
       </c>
       <c r="E28">
-        <v>-90.50000000000003</v>
+        <v>-83.65000000000001</v>
       </c>
       <c r="F28">
-        <v>178.1</v>
+        <v>184.95</v>
       </c>
       <c r="G28">
         <v>16.2</v>
@@ -3583,28 +3583,28 @@
         <v>130.6</v>
       </c>
       <c r="M28">
-        <v>8.95843</v>
+        <v>9.302985</v>
       </c>
       <c r="N28">
-        <v>121.64157</v>
+        <v>121.297015</v>
       </c>
       <c r="O28">
-        <v>36.492471</v>
+        <v>36.38910449999999</v>
       </c>
       <c r="P28">
-        <v>85.14909900000001</v>
+        <v>84.90791049999999</v>
       </c>
       <c r="Q28">
-        <v>97.04909900000001</v>
+        <v>96.80791049999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1274002047384155</v>
+        <v>0.1282488682055193</v>
       </c>
       <c r="T28">
-        <v>1.187382405769448</v>
+        <v>1.199731493280793</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>14.57844733954499</v>
+        <v>14.03850484548776</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1031283737900291</v>
+        <v>0.1028259960736307</v>
       </c>
       <c r="C29">
-        <v>522.2077968969244</v>
+        <v>517.7900785865913</v>
       </c>
       <c r="D29">
-        <v>690.9577968969244</v>
+        <v>693.3900785865912</v>
       </c>
       <c r="E29">
-        <v>-83.65000000000001</v>
+        <v>-76.80000000000001</v>
       </c>
       <c r="F29">
-        <v>184.95</v>
+        <v>191.8</v>
       </c>
       <c r="G29">
         <v>16.2</v>
@@ -3665,28 +3665,28 @@
         <v>130.6</v>
       </c>
       <c r="M29">
-        <v>9.302985</v>
+        <v>9.647539999999999</v>
       </c>
       <c r="N29">
-        <v>121.297015</v>
+        <v>120.95246</v>
       </c>
       <c r="O29">
-        <v>36.38910449999999</v>
+        <v>36.285738</v>
       </c>
       <c r="P29">
-        <v>84.90791049999999</v>
+        <v>84.66672199999999</v>
       </c>
       <c r="Q29">
-        <v>96.80791049999999</v>
+        <v>96.566722</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1282488682055193</v>
+        <v>0.1291211056578205</v>
       </c>
       <c r="T29">
-        <v>1.199731493280793</v>
+        <v>1.212423611000787</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>14.03850484548776</v>
+        <v>13.53712967243463</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1028259960736307</v>
+        <v>0.1025236183572324</v>
       </c>
       <c r="C30">
-        <v>517.7900785865913</v>
+        <v>513.3895448078031</v>
       </c>
       <c r="D30">
-        <v>693.3900785865912</v>
+        <v>695.8395448078031</v>
       </c>
       <c r="E30">
-        <v>-76.80000000000001</v>
+        <v>-69.94999999999999</v>
       </c>
       <c r="F30">
-        <v>191.8</v>
+        <v>198.65</v>
       </c>
       <c r="G30">
         <v>16.2</v>
@@ -3747,28 +3747,28 @@
         <v>130.6</v>
       </c>
       <c r="M30">
-        <v>9.647539999999999</v>
+        <v>9.992095000000001</v>
       </c>
       <c r="N30">
-        <v>120.95246</v>
+        <v>120.607905</v>
       </c>
       <c r="O30">
-        <v>36.285738</v>
+        <v>36.1823715</v>
       </c>
       <c r="P30">
-        <v>84.66672199999999</v>
+        <v>84.4255335</v>
       </c>
       <c r="Q30">
-        <v>96.566722</v>
+        <v>96.32553350000001</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1291211056578205</v>
+        <v>0.1300179131792006</v>
       </c>
       <c r="T30">
-        <v>1.212423611000787</v>
+        <v>1.225473253163597</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>13.53712967243463</v>
+        <v>13.07033209752309</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1025236183572324</v>
+        <v>0.102536240640834</v>
       </c>
       <c r="C31">
-        <v>513.3895448078032</v>
+        <v>506.4369496057164</v>
       </c>
       <c r="D31">
-        <v>695.8395448078031</v>
+        <v>695.7369496057164</v>
       </c>
       <c r="E31">
-        <v>-69.95000000000005</v>
+        <v>-63.10000000000002</v>
       </c>
       <c r="F31">
-        <v>198.65</v>
+        <v>205.5</v>
       </c>
       <c r="G31">
         <v>16.2</v>
@@ -3829,45 +3829,45 @@
         <v>130.6</v>
       </c>
       <c r="M31">
-        <v>9.992094999999999</v>
+        <v>10.6449</v>
       </c>
       <c r="N31">
-        <v>120.607905</v>
+        <v>119.9551</v>
       </c>
       <c r="O31">
-        <v>36.1823715</v>
+        <v>35.98652999999999</v>
       </c>
       <c r="P31">
-        <v>84.4255335</v>
+        <v>83.96857</v>
       </c>
       <c r="Q31">
-        <v>96.32553350000001</v>
+        <v>95.86857000000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1300179131792006</v>
+        <v>0.1309403437726201</v>
       </c>
       <c r="T31">
-        <v>1.225473253163597</v>
+        <v>1.238895742245345</v>
       </c>
       <c r="U31">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V31">
         <v>0.3</v>
       </c>
       <c r="W31">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y31">
-        <v>13.07033209752309</v>
+        <v>12.26878599141373</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.102536240640834</v>
+        <v>0.1022443629244357</v>
       </c>
       <c r="C32">
-        <v>506.4369496057164</v>
+        <v>501.9671265465292</v>
       </c>
       <c r="D32">
-        <v>695.7369496057164</v>
+        <v>698.1171265465292</v>
       </c>
       <c r="E32">
-        <v>-63.10000000000002</v>
+        <v>-56.25000000000003</v>
       </c>
       <c r="F32">
-        <v>205.5</v>
+        <v>212.35</v>
       </c>
       <c r="G32">
         <v>16.2</v>
@@ -3911,28 +3911,28 @@
         <v>130.6</v>
       </c>
       <c r="M32">
-        <v>10.6449</v>
+        <v>10.99973</v>
       </c>
       <c r="N32">
-        <v>119.9551</v>
+        <v>119.60027</v>
       </c>
       <c r="O32">
-        <v>35.98652999999999</v>
+        <v>35.880081</v>
       </c>
       <c r="P32">
-        <v>83.96857</v>
+        <v>83.720189</v>
       </c>
       <c r="Q32">
-        <v>95.86857000000001</v>
+        <v>95.62018900000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1309403437726201</v>
+        <v>0.1318895114846894</v>
       </c>
       <c r="T32">
-        <v>1.238895742245345</v>
+        <v>1.252707288981637</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>12.26878599141373</v>
+        <v>11.87301870136812</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1022443629244357</v>
+        <v>0.1019524852080373</v>
       </c>
       <c r="C33">
-        <v>501.9671265465292</v>
+        <v>497.5136449798978</v>
       </c>
       <c r="D33">
-        <v>698.1171265465292</v>
+        <v>700.5136449798978</v>
       </c>
       <c r="E33">
-        <v>-56.25000000000003</v>
+        <v>-49.40000000000001</v>
       </c>
       <c r="F33">
-        <v>212.35</v>
+        <v>219.2</v>
       </c>
       <c r="G33">
         <v>16.2</v>
@@ -3993,28 +3993,28 @@
         <v>130.6</v>
       </c>
       <c r="M33">
-        <v>10.99973</v>
+        <v>11.35456</v>
       </c>
       <c r="N33">
-        <v>119.60027</v>
+        <v>119.24544</v>
       </c>
       <c r="O33">
-        <v>35.880081</v>
+        <v>35.77363199999999</v>
       </c>
       <c r="P33">
-        <v>83.720189</v>
+        <v>83.471808</v>
       </c>
       <c r="Q33">
-        <v>95.62018900000001</v>
+        <v>95.371808</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1318895114846894</v>
+        <v>0.1328665958941725</v>
       </c>
       <c r="T33">
-        <v>1.252707288981637</v>
+        <v>1.26692505768076</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>11.87301870136812</v>
+        <v>11.50198686695037</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1019524852080373</v>
+        <v>0.101660607491639</v>
       </c>
       <c r="C34">
-        <v>497.5136449798978</v>
+        <v>493.0766737783021</v>
       </c>
       <c r="D34">
-        <v>700.5136449798978</v>
+        <v>702.9266737783021</v>
       </c>
       <c r="E34">
-        <v>-49.40000000000001</v>
+        <v>-42.55000000000001</v>
       </c>
       <c r="F34">
-        <v>219.2</v>
+        <v>226.05</v>
       </c>
       <c r="G34">
         <v>16.2</v>
@@ -4075,28 +4075,28 @@
         <v>130.6</v>
       </c>
       <c r="M34">
-        <v>11.35456</v>
+        <v>11.70939</v>
       </c>
       <c r="N34">
-        <v>119.24544</v>
+        <v>118.89061</v>
       </c>
       <c r="O34">
-        <v>35.77363199999999</v>
+        <v>35.66718299999999</v>
       </c>
       <c r="P34">
-        <v>83.471808</v>
+        <v>83.223427</v>
       </c>
       <c r="Q34">
-        <v>95.371808</v>
+        <v>95.12342700000001</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1328665958941725</v>
+        <v>0.1338728470024463</v>
       </c>
       <c r="T34">
-        <v>1.26692505768076</v>
+        <v>1.281567237385828</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>11.50198686695037</v>
+        <v>11.15344181037612</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.101660607491639</v>
+        <v>0.1013687297752406</v>
       </c>
       <c r="C35">
-        <v>493.0766737783021</v>
+        <v>488.6563841490961</v>
       </c>
       <c r="D35">
-        <v>702.9266737783021</v>
+        <v>705.356384149096</v>
       </c>
       <c r="E35">
-        <v>-42.55000000000001</v>
+        <v>-35.70000000000002</v>
       </c>
       <c r="F35">
-        <v>226.05</v>
+        <v>232.9</v>
       </c>
       <c r="G35">
         <v>16.2</v>
@@ -4157,28 +4157,28 @@
         <v>130.6</v>
       </c>
       <c r="M35">
-        <v>11.70939</v>
+        <v>12.06422</v>
       </c>
       <c r="N35">
-        <v>118.89061</v>
+        <v>118.53578</v>
       </c>
       <c r="O35">
-        <v>35.66718299999999</v>
+        <v>35.560734</v>
       </c>
       <c r="P35">
-        <v>83.223427</v>
+        <v>82.97504599999999</v>
       </c>
       <c r="Q35">
-        <v>95.12342700000001</v>
+        <v>94.875046</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1338728470024463</v>
+        <v>0.1349095905685464</v>
       </c>
       <c r="T35">
-        <v>1.281567237385828</v>
+        <v>1.296653119506201</v>
       </c>
       <c r="U35">
         <v>0.0518</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>11.15344181037612</v>
+        <v>10.82539940418858</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1013687297752406</v>
+        <v>0.1010768520588423</v>
       </c>
       <c r="C36">
-        <v>488.6563841490961</v>
+        <v>484.2529496749995</v>
       </c>
       <c r="D36">
-        <v>705.356384149096</v>
+        <v>707.8029496749995</v>
       </c>
       <c r="E36">
-        <v>-35.70000000000002</v>
+        <v>-28.84999999999999</v>
       </c>
       <c r="F36">
-        <v>232.9</v>
+        <v>239.75</v>
       </c>
       <c r="G36">
         <v>16.2</v>
@@ -4239,28 +4239,28 @@
         <v>130.6</v>
       </c>
       <c r="M36">
-        <v>12.06422</v>
+        <v>12.41905</v>
       </c>
       <c r="N36">
-        <v>118.53578</v>
+        <v>118.18095</v>
       </c>
       <c r="O36">
-        <v>35.560734</v>
+        <v>35.454285</v>
       </c>
       <c r="P36">
-        <v>82.97504599999999</v>
+        <v>82.726665</v>
       </c>
       <c r="Q36">
-        <v>94.875046</v>
+        <v>94.626665</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1349095905685464</v>
+        <v>0.1359782339366804</v>
       </c>
       <c r="T36">
-        <v>1.296653119506201</v>
+        <v>1.312203182614893</v>
       </c>
       <c r="U36">
         <v>0.0518</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>10.82539940418858</v>
+        <v>10.51610227835462</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1010768520588423</v>
+        <v>0.1007849743424439</v>
       </c>
       <c r="C37">
-        <v>484.2529496749995</v>
+        <v>479.8665463554374</v>
       </c>
       <c r="D37">
-        <v>707.8029496749995</v>
+        <v>710.2665463554374</v>
       </c>
       <c r="E37">
-        <v>-28.84999999999999</v>
+        <v>-22</v>
       </c>
       <c r="F37">
-        <v>239.75</v>
+        <v>246.6</v>
       </c>
       <c r="G37">
         <v>16.2</v>
@@ -4321,28 +4321,28 @@
         <v>130.6</v>
       </c>
       <c r="M37">
-        <v>12.41905</v>
+        <v>12.77388</v>
       </c>
       <c r="N37">
-        <v>118.18095</v>
+        <v>117.82612</v>
       </c>
       <c r="O37">
-        <v>35.454285</v>
+        <v>35.34783599999999</v>
       </c>
       <c r="P37">
-        <v>82.726665</v>
+        <v>82.478284</v>
       </c>
       <c r="Q37">
-        <v>94.626665</v>
+        <v>94.37828400000001</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1359782339366804</v>
+        <v>0.1370802724100686</v>
       </c>
       <c r="T37">
-        <v>1.312203182614893</v>
+        <v>1.328239185195731</v>
       </c>
       <c r="U37">
         <v>0.0518</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>10.51610227835462</v>
+        <v>10.22398832617811</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1007849743424439</v>
+        <v>0.1004930966260456</v>
       </c>
       <c r="C38">
-        <v>479.8665463554374</v>
+        <v>475.4973526487467</v>
       </c>
       <c r="D38">
-        <v>710.2665463554374</v>
+        <v>712.7473526487466</v>
       </c>
       <c r="E38">
-        <v>-22.00000000000003</v>
+        <v>-15.15000000000003</v>
       </c>
       <c r="F38">
-        <v>246.6</v>
+        <v>253.45</v>
       </c>
       <c r="G38">
         <v>16.2</v>
@@ -4403,28 +4403,28 @@
         <v>130.6</v>
       </c>
       <c r="M38">
-        <v>12.77388</v>
+        <v>13.12871</v>
       </c>
       <c r="N38">
-        <v>117.82612</v>
+        <v>117.47129</v>
       </c>
       <c r="O38">
-        <v>35.34783599999999</v>
+        <v>35.241387</v>
       </c>
       <c r="P38">
-        <v>82.478284</v>
+        <v>82.22990300000001</v>
       </c>
       <c r="Q38">
-        <v>94.37828400000001</v>
+        <v>94.12990300000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1370802724100686</v>
+        <v>0.1382172962318183</v>
       </c>
       <c r="T38">
-        <v>1.328239185195731</v>
+        <v>1.34478426722358</v>
       </c>
       <c r="U38">
         <v>0.0518</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>10.22398832617811</v>
+        <v>9.947664317362483</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1004930966260456</v>
+        <v>0.1006534189096472</v>
       </c>
       <c r="C39">
-        <v>475.4973526487467</v>
+        <v>467.2825569104434</v>
       </c>
       <c r="D39">
-        <v>712.7473526487466</v>
+        <v>711.3825569104433</v>
       </c>
       <c r="E39">
-        <v>-15.15000000000003</v>
+        <v>-8.300000000000011</v>
       </c>
       <c r="F39">
-        <v>253.45</v>
+        <v>260.3</v>
       </c>
       <c r="G39">
         <v>16.2</v>
@@ -4485,45 +4485,45 @@
         <v>130.6</v>
       </c>
       <c r="M39">
-        <v>13.12871</v>
+        <v>13.92605</v>
       </c>
       <c r="N39">
-        <v>117.47129</v>
+        <v>116.67395</v>
       </c>
       <c r="O39">
-        <v>35.241387</v>
+        <v>35.002185</v>
       </c>
       <c r="P39">
-        <v>82.22990300000001</v>
+        <v>81.67176499999999</v>
       </c>
       <c r="Q39">
-        <v>94.12990300000001</v>
+        <v>93.571765</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1382172962318183</v>
+        <v>0.1393909982413665</v>
       </c>
       <c r="T39">
-        <v>1.34478426722358</v>
+        <v>1.361863061574908</v>
       </c>
       <c r="U39">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V39">
         <v>0.3</v>
       </c>
       <c r="W39">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y39">
-        <v>9.947664317362483</v>
+        <v>9.378107934410689</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1006534189096472</v>
+        <v>0.1003734411932489</v>
       </c>
       <c r="C40">
-        <v>467.2825569104434</v>
+        <v>462.8193761635975</v>
       </c>
       <c r="D40">
-        <v>711.3825569104433</v>
+        <v>713.7693761635975</v>
       </c>
       <c r="E40">
-        <v>-8.300000000000011</v>
+        <v>-1.449999999999989</v>
       </c>
       <c r="F40">
-        <v>260.3</v>
+        <v>267.15</v>
       </c>
       <c r="G40">
         <v>16.2</v>
@@ -4567,28 +4567,28 @@
         <v>130.6</v>
       </c>
       <c r="M40">
-        <v>13.92605</v>
+        <v>14.292525</v>
       </c>
       <c r="N40">
-        <v>116.67395</v>
+        <v>116.307475</v>
       </c>
       <c r="O40">
-        <v>35.002185</v>
+        <v>34.89224249999999</v>
       </c>
       <c r="P40">
-        <v>81.67176499999999</v>
+        <v>81.4152325</v>
       </c>
       <c r="Q40">
-        <v>93.571765</v>
+        <v>93.31523250000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1393909982413665</v>
+        <v>0.1406031822840145</v>
       </c>
       <c r="T40">
-        <v>1.361863061574908</v>
+        <v>1.379501816396772</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>9.378107934410689</v>
+        <v>9.137643628400159</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1003734411932489</v>
+        <v>0.1000934634768505</v>
       </c>
       <c r="C41">
-        <v>462.8193761635975</v>
+        <v>458.3722657704778</v>
       </c>
       <c r="D41">
-        <v>713.7693761635975</v>
+        <v>716.1722657704778</v>
       </c>
       <c r="E41">
-        <v>-1.449999999999989</v>
+        <v>5.399999999999977</v>
       </c>
       <c r="F41">
-        <v>267.15</v>
+        <v>274</v>
       </c>
       <c r="G41">
         <v>16.2</v>
@@ -4649,28 +4649,28 @@
         <v>130.6</v>
       </c>
       <c r="M41">
-        <v>14.292525</v>
+        <v>14.659</v>
       </c>
       <c r="N41">
-        <v>116.307475</v>
+        <v>115.941</v>
       </c>
       <c r="O41">
-        <v>34.89224249999999</v>
+        <v>34.7823</v>
       </c>
       <c r="P41">
-        <v>81.4152325</v>
+        <v>81.15870000000001</v>
       </c>
       <c r="Q41">
-        <v>93.31523250000001</v>
+        <v>93.05870000000002</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1406031822840145</v>
+        <v>0.1418557724614175</v>
       </c>
       <c r="T41">
-        <v>1.379501816396772</v>
+        <v>1.397728529712698</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>9.137643628400159</v>
+        <v>8.909202537690156</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1000934634768505</v>
+        <v>0.09981348576045213</v>
       </c>
       <c r="C42">
-        <v>458.3722657704778</v>
+        <v>453.9413885808391</v>
       </c>
       <c r="D42">
-        <v>716.1722657704778</v>
+        <v>718.5913885808391</v>
       </c>
       <c r="E42">
-        <v>5.399999999999977</v>
+        <v>12.25</v>
       </c>
       <c r="F42">
-        <v>274</v>
+        <v>280.85</v>
       </c>
       <c r="G42">
         <v>16.2</v>
@@ -4731,28 +4731,28 @@
         <v>130.6</v>
       </c>
       <c r="M42">
-        <v>14.659</v>
+        <v>15.025475</v>
       </c>
       <c r="N42">
-        <v>115.941</v>
+        <v>115.574525</v>
       </c>
       <c r="O42">
-        <v>34.7823</v>
+        <v>34.6723575</v>
       </c>
       <c r="P42">
-        <v>81.15870000000001</v>
+        <v>80.90216749999999</v>
       </c>
       <c r="Q42">
-        <v>93.05870000000002</v>
+        <v>92.8021675</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1418557724614175</v>
+        <v>0.1431508233228002</v>
       </c>
       <c r="T42">
-        <v>1.397728529712698</v>
+        <v>1.416573097717299</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.909202537690156</v>
+        <v>8.691904914819665</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09981348576045213</v>
+        <v>0.09953350804405378</v>
       </c>
       <c r="C43">
-        <v>453.9413885808391</v>
+        <v>449.5269096522217</v>
       </c>
       <c r="D43">
-        <v>718.5913885808391</v>
+        <v>721.0269096522217</v>
       </c>
       <c r="E43">
-        <v>12.25</v>
+        <v>19.10000000000002</v>
       </c>
       <c r="F43">
-        <v>280.85</v>
+        <v>287.7</v>
       </c>
       <c r="G43">
         <v>16.2</v>
@@ -4813,28 +4813,28 @@
         <v>130.6</v>
       </c>
       <c r="M43">
-        <v>15.025475</v>
+        <v>15.39195</v>
       </c>
       <c r="N43">
-        <v>115.574525</v>
+        <v>115.20805</v>
       </c>
       <c r="O43">
-        <v>34.6723575</v>
+        <v>34.56241499999999</v>
       </c>
       <c r="P43">
-        <v>80.90216749999999</v>
+        <v>80.645635</v>
       </c>
       <c r="Q43">
-        <v>92.8021675</v>
+        <v>92.545635</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1431508233228002</v>
+        <v>0.1444905311104376</v>
       </c>
       <c r="T43">
-        <v>1.416573097717299</v>
+        <v>1.436067478411714</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>8.691904914819665</v>
+        <v>8.484954797800146</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09953350804405381</v>
+        <v>0.09925353032765544</v>
       </c>
       <c r="C44">
-        <v>449.5269096522214</v>
+        <v>445.128996287494</v>
       </c>
       <c r="D44">
-        <v>721.0269096522213</v>
+        <v>723.4789962874939</v>
       </c>
       <c r="E44">
-        <v>19.09999999999997</v>
+        <v>25.94999999999999</v>
       </c>
       <c r="F44">
-        <v>287.7</v>
+        <v>294.55</v>
       </c>
       <c r="G44">
         <v>16.2</v>
@@ -4895,28 +4895,28 @@
         <v>130.6</v>
       </c>
       <c r="M44">
-        <v>15.39195</v>
+        <v>15.758425</v>
       </c>
       <c r="N44">
-        <v>115.20805</v>
+        <v>114.841575</v>
       </c>
       <c r="O44">
-        <v>34.562415</v>
+        <v>34.4524725</v>
       </c>
       <c r="P44">
-        <v>80.645635</v>
+        <v>80.38910249999999</v>
       </c>
       <c r="Q44">
-        <v>92.545635</v>
+        <v>92.2891025</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1444905311104376</v>
+        <v>0.1458772461888692</v>
       </c>
       <c r="T44">
-        <v>1.436067478411713</v>
+        <v>1.456245872463827</v>
       </c>
       <c r="U44">
         <v>0.0535</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>8.48495479780015</v>
+        <v>8.287630267618749</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09925353032765544</v>
+        <v>0.09897355261125709</v>
       </c>
       <c r="C45">
-        <v>445.128996287494</v>
+        <v>440.7478180731621</v>
       </c>
       <c r="D45">
-        <v>723.4789962874939</v>
+        <v>725.947818073162</v>
       </c>
       <c r="E45">
-        <v>25.94999999999999</v>
+        <v>32.79999999999995</v>
       </c>
       <c r="F45">
-        <v>294.55</v>
+        <v>301.4</v>
       </c>
       <c r="G45">
         <v>16.2</v>
@@ -4977,28 +4977,28 @@
         <v>130.6</v>
       </c>
       <c r="M45">
-        <v>15.758425</v>
+        <v>16.1249</v>
       </c>
       <c r="N45">
-        <v>114.841575</v>
+        <v>114.4751</v>
       </c>
       <c r="O45">
-        <v>34.4524725</v>
+        <v>34.34253</v>
       </c>
       <c r="P45">
-        <v>80.38910249999999</v>
+        <v>80.13257</v>
       </c>
       <c r="Q45">
-        <v>92.2891025</v>
+        <v>92.03257000000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1458772461888692</v>
+        <v>0.1473134868058162</v>
       </c>
       <c r="T45">
-        <v>1.456245872463827</v>
+        <v>1.477144923446373</v>
       </c>
       <c r="U45">
         <v>0.0535</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>8.287630267618749</v>
+        <v>8.099275034263778</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09897355261125709</v>
+        <v>0.09869357489485875</v>
       </c>
       <c r="C46">
-        <v>440.7478180731621</v>
+        <v>436.3835469184667</v>
       </c>
       <c r="D46">
-        <v>725.947818073162</v>
+        <v>728.4335469184666</v>
       </c>
       <c r="E46">
-        <v>32.79999999999995</v>
+        <v>39.64999999999998</v>
       </c>
       <c r="F46">
-        <v>301.4</v>
+        <v>308.25</v>
       </c>
       <c r="G46">
         <v>16.2</v>
@@ -5059,28 +5059,28 @@
         <v>130.6</v>
       </c>
       <c r="M46">
-        <v>16.1249</v>
+        <v>16.491375</v>
       </c>
       <c r="N46">
-        <v>114.4751</v>
+        <v>114.108625</v>
       </c>
       <c r="O46">
-        <v>34.34253</v>
+        <v>34.23258749999999</v>
       </c>
       <c r="P46">
-        <v>80.13257</v>
+        <v>79.8760375</v>
       </c>
       <c r="Q46">
-        <v>92.03257000000001</v>
+        <v>91.7760375</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1473134868058162</v>
+        <v>0.1488019543542886</v>
       </c>
       <c r="T46">
-        <v>1.477144923446373</v>
+        <v>1.498803939919194</v>
       </c>
       <c r="U46">
         <v>0.0535</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>8.099275034263778</v>
+        <v>7.919291144613471</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09869357489485875</v>
+        <v>0.09841359717846038</v>
       </c>
       <c r="C47">
-        <v>436.3835469184667</v>
+        <v>432.0363570952866</v>
       </c>
       <c r="D47">
-        <v>728.4335469184666</v>
+        <v>730.9363570952866</v>
       </c>
       <c r="E47">
-        <v>39.64999999999998</v>
+        <v>46.5</v>
       </c>
       <c r="F47">
-        <v>308.25</v>
+        <v>315.1</v>
       </c>
       <c r="G47">
         <v>16.2</v>
@@ -5141,28 +5141,28 @@
         <v>130.6</v>
       </c>
       <c r="M47">
-        <v>16.491375</v>
+        <v>16.85785</v>
       </c>
       <c r="N47">
-        <v>114.108625</v>
+        <v>113.74215</v>
       </c>
       <c r="O47">
-        <v>34.23258749999999</v>
+        <v>34.122645</v>
       </c>
       <c r="P47">
-        <v>79.8760375</v>
+        <v>79.619505</v>
       </c>
       <c r="Q47">
-        <v>91.7760375</v>
+        <v>91.51950500000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1488019543542886</v>
+        <v>0.1503455503304822</v>
       </c>
       <c r="T47">
-        <v>1.498803939919194</v>
+        <v>1.521265142187304</v>
       </c>
       <c r="U47">
         <v>0.0535</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.919291144613471</v>
+        <v>7.747132641469701</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09841359717846038</v>
+        <v>0.09839681946206204</v>
       </c>
       <c r="C48">
-        <v>432.0363570952866</v>
+        <v>425.3368847686347</v>
       </c>
       <c r="D48">
-        <v>730.9363570952866</v>
+        <v>731.0868847686347</v>
       </c>
       <c r="E48">
-        <v>46.5</v>
+        <v>53.35000000000002</v>
       </c>
       <c r="F48">
-        <v>315.1</v>
+        <v>321.95</v>
       </c>
       <c r="G48">
         <v>16.2</v>
@@ -5223,45 +5223,45 @@
         <v>130.6</v>
       </c>
       <c r="M48">
-        <v>16.85785</v>
+        <v>17.481885</v>
       </c>
       <c r="N48">
-        <v>113.74215</v>
+        <v>113.118115</v>
       </c>
       <c r="O48">
-        <v>34.122645</v>
+        <v>33.93543449999999</v>
       </c>
       <c r="P48">
-        <v>79.619505</v>
+        <v>79.1826805</v>
       </c>
       <c r="Q48">
-        <v>91.51950500000001</v>
+        <v>91.08268050000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1503455503304822</v>
+        <v>0.1519473952114378</v>
       </c>
       <c r="T48">
-        <v>1.521265142187304</v>
+        <v>1.544573936993834</v>
       </c>
       <c r="U48">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V48">
         <v>0.3</v>
       </c>
       <c r="W48">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y48">
-        <v>7.747132641469701</v>
+        <v>7.470590271014824</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09839681946206204</v>
+        <v>0.09812244174566367</v>
       </c>
       <c r="C49">
-        <v>425.3368847686347</v>
+        <v>420.9573962298737</v>
       </c>
       <c r="D49">
-        <v>731.0868847686347</v>
+        <v>733.5573962298737</v>
       </c>
       <c r="E49">
-        <v>53.35000000000002</v>
+        <v>60.19999999999999</v>
       </c>
       <c r="F49">
-        <v>321.95</v>
+        <v>328.8</v>
       </c>
       <c r="G49">
         <v>16.2</v>
@@ -5305,28 +5305,28 @@
         <v>130.6</v>
       </c>
       <c r="M49">
-        <v>17.481885</v>
+        <v>17.85384</v>
       </c>
       <c r="N49">
-        <v>113.118115</v>
+        <v>112.74616</v>
       </c>
       <c r="O49">
-        <v>33.93543449999999</v>
+        <v>33.823848</v>
       </c>
       <c r="P49">
-        <v>79.1826805</v>
+        <v>78.92231199999999</v>
       </c>
       <c r="Q49">
-        <v>91.08268050000001</v>
+        <v>90.822312</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1519473952114378</v>
+        <v>0.1536108495108917</v>
       </c>
       <c r="T49">
-        <v>1.544573936993834</v>
+        <v>1.568779223908307</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>7.470590271014824</v>
+        <v>7.314952973702015</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09812244174566367</v>
+        <v>0.09784806402926531</v>
       </c>
       <c r="C50">
-        <v>420.9573962298737</v>
+        <v>416.5946611627713</v>
       </c>
       <c r="D50">
-        <v>733.5573962298737</v>
+        <v>736.0446611627713</v>
       </c>
       <c r="E50">
-        <v>60.19999999999999</v>
+        <v>67.04999999999995</v>
       </c>
       <c r="F50">
-        <v>328.8</v>
+        <v>335.65</v>
       </c>
       <c r="G50">
         <v>16.2</v>
@@ -5387,28 +5387,28 @@
         <v>130.6</v>
       </c>
       <c r="M50">
-        <v>17.85384</v>
+        <v>18.225795</v>
       </c>
       <c r="N50">
-        <v>112.74616</v>
+        <v>112.374205</v>
       </c>
       <c r="O50">
-        <v>33.823848</v>
+        <v>33.7122615</v>
       </c>
       <c r="P50">
-        <v>78.92231199999999</v>
+        <v>78.66194349999999</v>
       </c>
       <c r="Q50">
-        <v>90.822312</v>
+        <v>90.5619435</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1536108495108917</v>
+        <v>0.1553395373122849</v>
       </c>
       <c r="T50">
-        <v>1.568779223908307</v>
+        <v>1.593933737760603</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>7.314952973702015</v>
+        <v>7.165668219136669</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09784806402926531</v>
+        <v>0.09757368631286695</v>
       </c>
       <c r="C51">
-        <v>416.5946611627713</v>
+        <v>412.2488505645581</v>
       </c>
       <c r="D51">
-        <v>736.0446611627713</v>
+        <v>738.5488505645581</v>
       </c>
       <c r="E51">
-        <v>67.04999999999995</v>
+        <v>73.89999999999998</v>
       </c>
       <c r="F51">
-        <v>335.65</v>
+        <v>342.5</v>
       </c>
       <c r="G51">
         <v>16.2</v>
@@ -5469,28 +5469,28 @@
         <v>130.6</v>
       </c>
       <c r="M51">
-        <v>18.225795</v>
+        <v>18.59775</v>
       </c>
       <c r="N51">
-        <v>112.374205</v>
+        <v>112.00225</v>
       </c>
       <c r="O51">
-        <v>33.7122615</v>
+        <v>33.600675</v>
       </c>
       <c r="P51">
-        <v>78.66194349999999</v>
+        <v>78.40157499999999</v>
       </c>
       <c r="Q51">
-        <v>90.5619435</v>
+        <v>90.301575</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1553395373122849</v>
+        <v>0.1571373726257339</v>
       </c>
       <c r="T51">
-        <v>1.593933737760603</v>
+        <v>1.62009443216699</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>7.165668219136669</v>
+        <v>7.022354854753934</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09757368631286695</v>
+        <v>0.09729930859646861</v>
       </c>
       <c r="C52">
-        <v>412.2488505645581</v>
+        <v>407.9201377674923</v>
       </c>
       <c r="D52">
-        <v>738.5488505645581</v>
+        <v>741.0701377674923</v>
       </c>
       <c r="E52">
-        <v>73.89999999999998</v>
+        <v>80.75</v>
       </c>
       <c r="F52">
-        <v>342.5</v>
+        <v>349.35</v>
       </c>
       <c r="G52">
         <v>16.2</v>
@@ -5551,28 +5551,28 @@
         <v>130.6</v>
       </c>
       <c r="M52">
-        <v>18.59775</v>
+        <v>18.969705</v>
       </c>
       <c r="N52">
-        <v>112.00225</v>
+        <v>111.630295</v>
       </c>
       <c r="O52">
-        <v>33.600675</v>
+        <v>33.48908849999999</v>
       </c>
       <c r="P52">
-        <v>78.40157499999999</v>
+        <v>78.1412065</v>
       </c>
       <c r="Q52">
-        <v>90.301575</v>
+        <v>90.0412065</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1571373726257339</v>
+        <v>0.1590085889723849</v>
       </c>
       <c r="T52">
-        <v>1.62009443216699</v>
+        <v>1.647322910018536</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>7.022354854753934</v>
+        <v>6.884661622307779</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09729930859646861</v>
+        <v>0.09702493088007026</v>
       </c>
       <c r="C53">
-        <v>407.9201377674923</v>
+        <v>403.6086984788554</v>
       </c>
       <c r="D53">
-        <v>741.0701377674923</v>
+        <v>743.6086984788553</v>
       </c>
       <c r="E53">
-        <v>80.75</v>
+        <v>87.59999999999997</v>
       </c>
       <c r="F53">
-        <v>349.35</v>
+        <v>356.2</v>
       </c>
       <c r="G53">
         <v>16.2</v>
@@ -5633,28 +5633,28 @@
         <v>130.6</v>
       </c>
       <c r="M53">
-        <v>18.969705</v>
+        <v>19.34166</v>
       </c>
       <c r="N53">
-        <v>111.630295</v>
+        <v>111.25834</v>
       </c>
       <c r="O53">
-        <v>33.48908849999999</v>
+        <v>33.37750199999999</v>
       </c>
       <c r="P53">
-        <v>78.1412065</v>
+        <v>77.880838</v>
       </c>
       <c r="Q53">
-        <v>90.0412065</v>
+        <v>89.780838</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1590085889723849</v>
+        <v>0.160957772666813</v>
       </c>
       <c r="T53">
-        <v>1.647322910018536</v>
+        <v>1.675685907780563</v>
       </c>
       <c r="U53">
         <v>0.0543</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>6.884661622307779</v>
+        <v>6.752264283417245</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09702493088007026</v>
+        <v>0.0967505531636719</v>
       </c>
       <c r="C54">
-        <v>403.6086984788554</v>
+        <v>399.3147108217678</v>
       </c>
       <c r="D54">
-        <v>743.6086984788553</v>
+        <v>746.1647108217678</v>
       </c>
       <c r="E54">
-        <v>87.59999999999997</v>
+        <v>94.44999999999999</v>
       </c>
       <c r="F54">
-        <v>356.2</v>
+        <v>363.05</v>
       </c>
       <c r="G54">
         <v>16.2</v>
@@ -5715,28 +5715,28 @@
         <v>130.6</v>
       </c>
       <c r="M54">
-        <v>19.34166</v>
+        <v>19.713615</v>
       </c>
       <c r="N54">
-        <v>111.25834</v>
+        <v>110.886385</v>
       </c>
       <c r="O54">
-        <v>33.37750199999999</v>
+        <v>33.2659155</v>
       </c>
       <c r="P54">
-        <v>77.880838</v>
+        <v>77.62046949999998</v>
       </c>
       <c r="Q54">
-        <v>89.780838</v>
+        <v>89.52046949999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.160957772666813</v>
+        <v>0.1629899003482381</v>
       </c>
       <c r="T54">
-        <v>1.675685907780563</v>
+        <v>1.70525584161757</v>
       </c>
       <c r="U54">
         <v>0.0543</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>6.752264283417245</v>
+        <v>6.62486307052258</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.0967505531636719</v>
+        <v>0.09647617544727354</v>
       </c>
       <c r="C55">
-        <v>399.3147108217678</v>
+        <v>395.0383553768548</v>
       </c>
       <c r="D55">
-        <v>746.1647108217678</v>
+        <v>748.7383553768548</v>
       </c>
       <c r="E55">
-        <v>94.44999999999999</v>
+        <v>101.3</v>
       </c>
       <c r="F55">
-        <v>363.05</v>
+        <v>369.9</v>
       </c>
       <c r="G55">
         <v>16.2</v>
@@ -5797,28 +5797,28 @@
         <v>130.6</v>
       </c>
       <c r="M55">
-        <v>19.713615</v>
+        <v>20.08557</v>
       </c>
       <c r="N55">
-        <v>110.886385</v>
+        <v>110.51443</v>
       </c>
       <c r="O55">
-        <v>33.2659155</v>
+        <v>33.154329</v>
       </c>
       <c r="P55">
-        <v>77.62046949999998</v>
+        <v>77.36010099999999</v>
       </c>
       <c r="Q55">
-        <v>89.52046949999999</v>
+        <v>89.26010099999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1629899003482381</v>
+        <v>0.1651103814071164</v>
       </c>
       <c r="T55">
-        <v>1.70525584161757</v>
+        <v>1.736111424751839</v>
       </c>
       <c r="U55">
         <v>0.0543</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>6.62486307052258</v>
+        <v>6.502180421068458</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09647617544727354</v>
+        <v>0.0962017977308752</v>
       </c>
       <c r="C56">
-        <v>395.0383553768548</v>
+        <v>390.7798152247721</v>
       </c>
       <c r="D56">
-        <v>748.7383553768548</v>
+        <v>751.3298152247721</v>
       </c>
       <c r="E56">
-        <v>101.3</v>
+        <v>108.15</v>
       </c>
       <c r="F56">
-        <v>369.9</v>
+        <v>376.7500000000001</v>
       </c>
       <c r="G56">
         <v>16.2</v>
@@ -5879,28 +5879,28 @@
         <v>130.6</v>
       </c>
       <c r="M56">
-        <v>20.08557</v>
+        <v>20.457525</v>
       </c>
       <c r="N56">
-        <v>110.51443</v>
+        <v>110.142475</v>
       </c>
       <c r="O56">
-        <v>33.154329</v>
+        <v>33.0427425</v>
       </c>
       <c r="P56">
-        <v>77.36010099999999</v>
+        <v>77.09973249999999</v>
       </c>
       <c r="Q56">
-        <v>89.26010099999999</v>
+        <v>88.99973249999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1651103814071164</v>
+        <v>0.1673251060686116</v>
       </c>
       <c r="T56">
-        <v>1.736111424751839</v>
+        <v>1.768338367136519</v>
       </c>
       <c r="U56">
         <v>0.0543</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>6.502180421068458</v>
+        <v>6.383958958867212</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.0962017977308752</v>
+        <v>0.09592742001447684</v>
       </c>
       <c r="C57">
-        <v>390.7798152247721</v>
+        <v>386.5392759896234</v>
       </c>
       <c r="D57">
-        <v>751.3298152247721</v>
+        <v>753.9392759896234</v>
       </c>
       <c r="E57">
-        <v>108.15</v>
+        <v>115</v>
       </c>
       <c r="F57">
-        <v>376.7500000000001</v>
+        <v>383.6</v>
       </c>
       <c r="G57">
         <v>16.2</v>
@@ -5961,28 +5961,28 @@
         <v>130.6</v>
       </c>
       <c r="M57">
-        <v>20.457525</v>
+        <v>20.82948</v>
       </c>
       <c r="N57">
-        <v>110.142475</v>
+        <v>109.77052</v>
       </c>
       <c r="O57">
-        <v>33.0427425</v>
+        <v>32.93115599999999</v>
       </c>
       <c r="P57">
-        <v>77.09973249999999</v>
+        <v>76.83936399999999</v>
       </c>
       <c r="Q57">
-        <v>88.99973249999999</v>
+        <v>88.73936399999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1673251060686116</v>
+        <v>0.1696405000329019</v>
       </c>
       <c r="T57">
-        <v>1.768338367136519</v>
+        <v>1.802030170538685</v>
       </c>
       <c r="U57">
         <v>0.0543</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>6.383958958867212</v>
+        <v>6.269959691744584</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09592742001447684</v>
+        <v>0.09565304229807847</v>
       </c>
       <c r="C58">
-        <v>386.5392759896234</v>
+        <v>382.3169258832803</v>
       </c>
       <c r="D58">
-        <v>753.9392759896234</v>
+        <v>756.5669258832803</v>
       </c>
       <c r="E58">
-        <v>115</v>
+        <v>121.85</v>
       </c>
       <c r="F58">
-        <v>383.6</v>
+        <v>390.45</v>
       </c>
       <c r="G58">
         <v>16.2</v>
@@ -6043,28 +6043,28 @@
         <v>130.6</v>
       </c>
       <c r="M58">
-        <v>20.82948</v>
+        <v>21.201435</v>
       </c>
       <c r="N58">
-        <v>109.77052</v>
+        <v>109.398565</v>
       </c>
       <c r="O58">
-        <v>32.93115599999999</v>
+        <v>32.81956949999999</v>
       </c>
       <c r="P58">
-        <v>76.83936399999999</v>
+        <v>76.57899549999999</v>
       </c>
       <c r="Q58">
-        <v>88.73936399999999</v>
+        <v>88.4789955</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1696405000329019</v>
+        <v>0.1720635867397174</v>
       </c>
       <c r="T58">
-        <v>1.802030170538685</v>
+        <v>1.837289034564207</v>
       </c>
       <c r="U58">
         <v>0.0543</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>6.269959691744584</v>
+        <v>6.15996039890696</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09565304229807847</v>
+        <v>0.09578466458168014</v>
       </c>
       <c r="C59">
-        <v>382.3169258832803</v>
+        <v>374.2041287877407</v>
       </c>
       <c r="D59">
-        <v>756.5669258832803</v>
+        <v>755.3041287877408</v>
       </c>
       <c r="E59">
-        <v>121.85</v>
+        <v>128.7</v>
       </c>
       <c r="F59">
-        <v>390.45</v>
+        <v>397.3000000000001</v>
       </c>
       <c r="G59">
         <v>16.2</v>
@@ -6125,45 +6125,45 @@
         <v>130.6</v>
       </c>
       <c r="M59">
-        <v>21.201435</v>
+        <v>21.97069</v>
       </c>
       <c r="N59">
-        <v>109.398565</v>
+        <v>108.62931</v>
       </c>
       <c r="O59">
-        <v>32.81956949999999</v>
+        <v>32.588793</v>
       </c>
       <c r="P59">
-        <v>76.57899549999999</v>
+        <v>76.04051699999999</v>
       </c>
       <c r="Q59">
-        <v>88.4789955</v>
+        <v>87.940517</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1720635867397174</v>
+        <v>0.1746020585278099</v>
       </c>
       <c r="T59">
-        <v>1.837289034564207</v>
+        <v>1.874226892114754</v>
       </c>
       <c r="U59">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V59">
         <v>0.3</v>
       </c>
       <c r="W59">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y59">
-        <v>6.15996039890696</v>
+        <v>5.944283042544407</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09578466458168014</v>
+        <v>0.09551728686528177</v>
       </c>
       <c r="C60">
-        <v>374.2041287877408</v>
+        <v>369.9238079875903</v>
       </c>
       <c r="D60">
-        <v>755.3041287877408</v>
+        <v>757.8738079875902</v>
       </c>
       <c r="E60">
-        <v>128.6999999999999</v>
+        <v>135.55</v>
       </c>
       <c r="F60">
-        <v>397.3</v>
+        <v>404.15</v>
       </c>
       <c r="G60">
         <v>16.2</v>
@@ -6207,28 +6207,28 @@
         <v>130.6</v>
       </c>
       <c r="M60">
-        <v>21.97069</v>
+        <v>22.349495</v>
       </c>
       <c r="N60">
-        <v>108.62931</v>
+        <v>108.250505</v>
       </c>
       <c r="O60">
-        <v>32.588793</v>
+        <v>32.4751515</v>
       </c>
       <c r="P60">
-        <v>76.04051699999999</v>
+        <v>75.77535349999999</v>
       </c>
       <c r="Q60">
-        <v>87.940517</v>
+        <v>87.6753535</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1746020585278098</v>
+        <v>0.1772643582080043</v>
       </c>
       <c r="T60">
-        <v>1.874226892114753</v>
+        <v>1.912966596375083</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.944283042544408</v>
+        <v>5.843532482501282</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09551728686528177</v>
+        <v>0.09524990914888343</v>
       </c>
       <c r="C61">
-        <v>369.9238079875903</v>
+        <v>365.6610318904718</v>
       </c>
       <c r="D61">
-        <v>757.8738079875902</v>
+        <v>760.4610318904718</v>
       </c>
       <c r="E61">
-        <v>135.55</v>
+        <v>142.4</v>
       </c>
       <c r="F61">
-        <v>404.15</v>
+        <v>411</v>
       </c>
       <c r="G61">
         <v>16.2</v>
@@ -6289,28 +6289,28 @@
         <v>130.6</v>
       </c>
       <c r="M61">
-        <v>22.349495</v>
+        <v>22.7283</v>
       </c>
       <c r="N61">
-        <v>108.250505</v>
+        <v>107.8717</v>
       </c>
       <c r="O61">
-        <v>32.4751515</v>
+        <v>32.36151</v>
       </c>
       <c r="P61">
-        <v>75.77535349999999</v>
+        <v>75.51018999999999</v>
       </c>
       <c r="Q61">
-        <v>87.6753535</v>
+        <v>87.41019</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1772643582080043</v>
+        <v>0.1800597728722086</v>
       </c>
       <c r="T61">
-        <v>1.912966596375083</v>
+        <v>1.953643285848429</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.843532482501282</v>
+        <v>5.746140274459594</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09524990914888343</v>
+        <v>0.09498253143248507</v>
       </c>
       <c r="C62">
-        <v>365.6610318904718</v>
+        <v>361.4159807938095</v>
       </c>
       <c r="D62">
-        <v>760.4610318904718</v>
+        <v>763.0659807938094</v>
       </c>
       <c r="E62">
-        <v>142.4</v>
+        <v>149.2499999999999</v>
       </c>
       <c r="F62">
-        <v>411</v>
+        <v>417.85</v>
       </c>
       <c r="G62">
         <v>16.2</v>
@@ -6371,28 +6371,28 @@
         <v>130.6</v>
       </c>
       <c r="M62">
-        <v>22.7283</v>
+        <v>23.107105</v>
       </c>
       <c r="N62">
-        <v>107.8717</v>
+        <v>107.492895</v>
       </c>
       <c r="O62">
-        <v>32.36151</v>
+        <v>32.2478685</v>
       </c>
       <c r="P62">
-        <v>75.51018999999999</v>
+        <v>75.24502649999999</v>
       </c>
       <c r="Q62">
-        <v>87.41019</v>
+        <v>87.1450265</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1800597728722086</v>
+        <v>0.1829985421345771</v>
       </c>
       <c r="T62">
-        <v>1.953643285848429</v>
+        <v>1.996405959397332</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.746140274459594</v>
+        <v>5.651941253566814</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.09498253143248507</v>
+        <v>0.09471515371608671</v>
       </c>
       <c r="C63">
-        <v>361.4159807938095</v>
+        <v>357.1888374739435</v>
       </c>
       <c r="D63">
-        <v>763.0659807938094</v>
+        <v>765.6888374739434</v>
       </c>
       <c r="E63">
-        <v>149.2499999999999</v>
+        <v>156.1</v>
       </c>
       <c r="F63">
-        <v>417.85</v>
+        <v>424.7</v>
       </c>
       <c r="G63">
         <v>16.2</v>
@@ -6453,28 +6453,28 @@
         <v>130.6</v>
       </c>
       <c r="M63">
-        <v>23.107105</v>
+        <v>23.48591</v>
       </c>
       <c r="N63">
-        <v>107.492895</v>
+        <v>107.11409</v>
       </c>
       <c r="O63">
-        <v>32.2478685</v>
+        <v>32.134227</v>
       </c>
       <c r="P63">
-        <v>75.24502649999999</v>
+        <v>74.97986299999999</v>
       </c>
       <c r="Q63">
-        <v>87.1450265</v>
+        <v>86.879863</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1829985421345771</v>
+        <v>0.1860919834633861</v>
       </c>
       <c r="T63">
-        <v>1.996405959397332</v>
+        <v>2.041419299975124</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.651941253566814</v>
+        <v>5.560780910767349</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09471515371608671</v>
+        <v>0.09444777599968836</v>
       </c>
       <c r="C64">
-        <v>357.1888374739435</v>
+        <v>352.9797872288819</v>
       </c>
       <c r="D64">
-        <v>765.6888374739434</v>
+        <v>768.3297872288819</v>
       </c>
       <c r="E64">
-        <v>156.1</v>
+        <v>162.95</v>
       </c>
       <c r="F64">
-        <v>424.7</v>
+        <v>431.55</v>
       </c>
       <c r="G64">
         <v>16.2</v>
@@ -6535,28 +6535,28 @@
         <v>130.6</v>
       </c>
       <c r="M64">
-        <v>23.48591</v>
+        <v>23.864715</v>
       </c>
       <c r="N64">
-        <v>107.11409</v>
+        <v>106.735285</v>
       </c>
       <c r="O64">
-        <v>32.134227</v>
+        <v>32.0205855</v>
       </c>
       <c r="P64">
-        <v>74.97986299999999</v>
+        <v>74.71469949999999</v>
       </c>
       <c r="Q64">
-        <v>86.879863</v>
+        <v>86.6146995</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1860919834633861</v>
+        <v>0.1893526378369956</v>
       </c>
       <c r="T64">
-        <v>2.041419299975124</v>
+        <v>2.088865794097662</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.560780910767349</v>
+        <v>5.472514547104375</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09444777599968836</v>
+        <v>0.09418039828329001</v>
       </c>
       <c r="C65">
-        <v>352.9797872288819</v>
+        <v>348.789017921938</v>
       </c>
       <c r="D65">
-        <v>768.3297872288819</v>
+        <v>770.9890179219379</v>
       </c>
       <c r="E65">
-        <v>162.95</v>
+        <v>169.8</v>
       </c>
       <c r="F65">
-        <v>431.55</v>
+        <v>438.4</v>
       </c>
       <c r="G65">
         <v>16.2</v>
@@ -6617,28 +6617,28 @@
         <v>130.6</v>
       </c>
       <c r="M65">
-        <v>23.864715</v>
+        <v>24.24352</v>
       </c>
       <c r="N65">
-        <v>106.735285</v>
+        <v>106.35648</v>
       </c>
       <c r="O65">
-        <v>32.0205855</v>
+        <v>31.906944</v>
       </c>
       <c r="P65">
-        <v>74.71469949999999</v>
+        <v>74.44953599999999</v>
       </c>
       <c r="Q65">
-        <v>86.6146995</v>
+        <v>86.349536</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1893526378369956</v>
+        <v>0.1927944396758056</v>
       </c>
       <c r="T65">
-        <v>2.088865794097662</v>
+        <v>2.13894820456034</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>5.472514547104375</v>
+        <v>5.387006507305869</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09418039828329001</v>
+        <v>0.09391302056689164</v>
       </c>
       <c r="C66">
-        <v>348.789017921938</v>
+        <v>344.6167200262782</v>
       </c>
       <c r="D66">
-        <v>770.9890179219379</v>
+        <v>773.6667200262782</v>
       </c>
       <c r="E66">
-        <v>169.8</v>
+        <v>176.65</v>
       </c>
       <c r="F66">
-        <v>438.4</v>
+        <v>445.25</v>
       </c>
       <c r="G66">
         <v>16.2</v>
@@ -6699,28 +6699,28 @@
         <v>130.6</v>
       </c>
       <c r="M66">
-        <v>24.24352</v>
+        <v>24.622325</v>
       </c>
       <c r="N66">
-        <v>106.35648</v>
+        <v>105.977675</v>
       </c>
       <c r="O66">
-        <v>31.906944</v>
+        <v>31.7933025</v>
       </c>
       <c r="P66">
-        <v>74.44953599999999</v>
+        <v>74.18437249999999</v>
       </c>
       <c r="Q66">
-        <v>86.349536</v>
+        <v>86.0843725</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1927944396758056</v>
+        <v>0.1964329159054047</v>
       </c>
       <c r="T66">
-        <v>2.13894820456034</v>
+        <v>2.191892467049457</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>5.387006507305869</v>
+        <v>5.304129484116548</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09391302056689164</v>
+        <v>0.0936456428504933</v>
       </c>
       <c r="C67">
-        <v>344.6167200262782</v>
+        <v>340.4630866704002</v>
       </c>
       <c r="D67">
-        <v>773.6667200262782</v>
+        <v>776.3630866704002</v>
       </c>
       <c r="E67">
-        <v>176.65</v>
+        <v>183.5</v>
       </c>
       <c r="F67">
-        <v>445.25</v>
+        <v>452.1</v>
       </c>
       <c r="G67">
         <v>16.2</v>
@@ -6781,28 +6781,28 @@
         <v>130.6</v>
       </c>
       <c r="M67">
-        <v>24.622325</v>
+        <v>25.00113</v>
       </c>
       <c r="N67">
-        <v>105.977675</v>
+        <v>105.59887</v>
       </c>
       <c r="O67">
-        <v>31.7933025</v>
+        <v>31.679661</v>
       </c>
       <c r="P67">
-        <v>74.18437249999999</v>
+        <v>73.919209</v>
       </c>
       <c r="Q67">
-        <v>86.0843725</v>
+        <v>85.819209</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1964329159054047</v>
+        <v>0.2002854201485097</v>
       </c>
       <c r="T67">
-        <v>2.191892467049457</v>
+        <v>2.247951097920287</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>5.304129484116548</v>
+        <v>5.223763885872358</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0936456428504933</v>
+        <v>0.09337826513409495</v>
       </c>
       <c r="C68">
-        <v>340.4630866704002</v>
+        <v>336.3283136845682</v>
       </c>
       <c r="D68">
-        <v>776.3630866704002</v>
+        <v>779.0783136845682</v>
       </c>
       <c r="E68">
-        <v>183.5</v>
+        <v>190.35</v>
       </c>
       <c r="F68">
-        <v>452.1</v>
+        <v>458.95</v>
       </c>
       <c r="G68">
         <v>16.2</v>
@@ -6863,28 +6863,28 @@
         <v>130.6</v>
       </c>
       <c r="M68">
-        <v>25.00113</v>
+        <v>25.379935</v>
       </c>
       <c r="N68">
-        <v>105.59887</v>
+        <v>105.220065</v>
       </c>
       <c r="O68">
-        <v>31.679661</v>
+        <v>31.5660195</v>
       </c>
       <c r="P68">
-        <v>73.919209</v>
+        <v>73.6540455</v>
       </c>
       <c r="Q68">
-        <v>85.819209</v>
+        <v>85.5540455</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2002854201485097</v>
+        <v>0.2043714094972574</v>
       </c>
       <c r="T68">
-        <v>2.247951097920287</v>
+        <v>2.307407221571168</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>5.223763885872358</v>
+        <v>5.145797260710084</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09337826513409495</v>
+        <v>0.0931108874176966</v>
       </c>
       <c r="C69">
-        <v>336.3283136845682</v>
+        <v>332.2125996482219</v>
       </c>
       <c r="D69">
-        <v>779.0783136845682</v>
+        <v>781.8125996482219</v>
       </c>
       <c r="E69">
-        <v>190.35</v>
+        <v>197.2</v>
       </c>
       <c r="F69">
-        <v>458.95</v>
+        <v>465.8</v>
       </c>
       <c r="G69">
         <v>16.2</v>
@@ -6945,28 +6945,28 @@
         <v>130.6</v>
       </c>
       <c r="M69">
-        <v>25.379935</v>
+        <v>25.75874</v>
       </c>
       <c r="N69">
-        <v>105.220065</v>
+        <v>104.84126</v>
       </c>
       <c r="O69">
-        <v>31.5660195</v>
+        <v>31.452378</v>
       </c>
       <c r="P69">
-        <v>73.6540455</v>
+        <v>73.388882</v>
       </c>
       <c r="Q69">
-        <v>85.5540455</v>
+        <v>85.288882</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2043714094972574</v>
+        <v>0.2087127731803019</v>
       </c>
       <c r="T69">
-        <v>2.307407221571168</v>
+        <v>2.370579352950229</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>5.145797260710084</v>
+        <v>5.070123771581994</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.0931108874176966</v>
+        <v>0.09284350970129823</v>
       </c>
       <c r="C70">
-        <v>332.2125996482219</v>
+        <v>328.116145938391</v>
       </c>
       <c r="D70">
-        <v>781.8125996482219</v>
+        <v>784.5661459383909</v>
       </c>
       <c r="E70">
-        <v>197.2</v>
+        <v>204.05</v>
       </c>
       <c r="F70">
-        <v>465.8</v>
+        <v>472.65</v>
       </c>
       <c r="G70">
         <v>16.2</v>
@@ -7027,28 +7027,28 @@
         <v>130.6</v>
       </c>
       <c r="M70">
-        <v>25.75874</v>
+        <v>26.137545</v>
       </c>
       <c r="N70">
-        <v>104.84126</v>
+        <v>104.462455</v>
       </c>
       <c r="O70">
-        <v>31.452378</v>
+        <v>31.3387365</v>
       </c>
       <c r="P70">
-        <v>73.388882</v>
+        <v>73.1237185</v>
       </c>
       <c r="Q70">
-        <v>85.288882</v>
+        <v>85.0237185</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2087127731803019</v>
+        <v>0.2133342248428976</v>
       </c>
       <c r="T70">
-        <v>2.370579352950229</v>
+        <v>2.437827105708584</v>
       </c>
       <c r="U70">
         <v>0.0553</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>5.070123771581994</v>
+        <v>4.996643716921385</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09284350970129823</v>
+        <v>0.09257613198489989</v>
       </c>
       <c r="C71">
-        <v>328.116145938391</v>
+        <v>324.0391567791336</v>
       </c>
       <c r="D71">
-        <v>784.5661459383909</v>
+        <v>787.3391567791336</v>
       </c>
       <c r="E71">
-        <v>204.05</v>
+        <v>210.9</v>
       </c>
       <c r="F71">
-        <v>472.65</v>
+        <v>479.5000000000001</v>
       </c>
       <c r="G71">
         <v>16.2</v>
@@ -7109,28 +7109,28 @@
         <v>130.6</v>
       </c>
       <c r="M71">
-        <v>26.137545</v>
+        <v>26.51635</v>
       </c>
       <c r="N71">
-        <v>104.462455</v>
+        <v>104.08365</v>
       </c>
       <c r="O71">
-        <v>31.3387365</v>
+        <v>31.225095</v>
       </c>
       <c r="P71">
-        <v>73.1237185</v>
+        <v>72.858555</v>
       </c>
       <c r="Q71">
-        <v>85.0237185</v>
+        <v>84.758555</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2133342248428976</v>
+        <v>0.2182637732829996</v>
       </c>
       <c r="T71">
-        <v>2.437827105708584</v>
+        <v>2.509558041984162</v>
       </c>
       <c r="U71">
         <v>0.0553</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.996643716921385</v>
+        <v>4.925263092393937</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09257613198489989</v>
+        <v>0.09230875426850155</v>
       </c>
       <c r="C72">
-        <v>324.0391567791336</v>
+        <v>319.9818392920304</v>
       </c>
       <c r="D72">
-        <v>787.3391567791336</v>
+        <v>790.1318392920305</v>
       </c>
       <c r="E72">
-        <v>210.9</v>
+        <v>217.7500000000001</v>
       </c>
       <c r="F72">
-        <v>479.5000000000001</v>
+        <v>486.3500000000001</v>
       </c>
       <c r="G72">
         <v>16.2</v>
@@ -7191,28 +7191,28 @@
         <v>130.6</v>
       </c>
       <c r="M72">
-        <v>26.51635</v>
+        <v>26.89515500000001</v>
       </c>
       <c r="N72">
-        <v>104.08365</v>
+        <v>103.704845</v>
       </c>
       <c r="O72">
-        <v>31.225095</v>
+        <v>31.1114535</v>
       </c>
       <c r="P72">
-        <v>72.858555</v>
+        <v>72.5933915</v>
       </c>
       <c r="Q72">
-        <v>84.758555</v>
+        <v>84.4933915</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2182637732829996</v>
+        <v>0.2235332905810398</v>
       </c>
       <c r="T72">
-        <v>2.509558041984162</v>
+        <v>2.586235939382194</v>
       </c>
       <c r="U72">
         <v>0.0553</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.925263092393937</v>
+        <v>4.855893189684164</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.09230875426850153</v>
+        <v>0.09204137655210318</v>
       </c>
       <c r="C73">
-        <v>319.9818392920307</v>
+        <v>315.9444035477524</v>
       </c>
       <c r="D73">
-        <v>790.1318392920306</v>
+        <v>792.9444035477524</v>
       </c>
       <c r="E73">
-        <v>217.7499999999999</v>
+        <v>224.6</v>
       </c>
       <c r="F73">
-        <v>486.35</v>
+        <v>493.2</v>
       </c>
       <c r="G73">
         <v>16.2</v>
@@ -7273,28 +7273,28 @@
         <v>130.6</v>
       </c>
       <c r="M73">
-        <v>26.895155</v>
+        <v>27.27396</v>
       </c>
       <c r="N73">
-        <v>103.704845</v>
+        <v>103.32604</v>
       </c>
       <c r="O73">
-        <v>31.1114535</v>
+        <v>30.997812</v>
       </c>
       <c r="P73">
-        <v>72.5933915</v>
+        <v>72.328228</v>
       </c>
       <c r="Q73">
-        <v>84.4933915</v>
+        <v>84.228228</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2235332905810398</v>
+        <v>0.2291792019717971</v>
       </c>
       <c r="T73">
-        <v>2.586235939382193</v>
+        <v>2.668390829451513</v>
       </c>
       <c r="U73">
         <v>0.0553</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.855893189684164</v>
+        <v>4.788450228716329</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.09204137655210318</v>
+        <v>0.09177399883570482</v>
       </c>
       <c r="C74">
-        <v>315.9444035477524</v>
+        <v>311.9270626187376</v>
       </c>
       <c r="D74">
-        <v>792.9444035477524</v>
+        <v>795.7770626187375</v>
       </c>
       <c r="E74">
-        <v>224.6</v>
+        <v>231.45</v>
       </c>
       <c r="F74">
-        <v>493.2</v>
+        <v>500.05</v>
       </c>
       <c r="G74">
         <v>16.2</v>
@@ -7355,28 +7355,28 @@
         <v>130.6</v>
       </c>
       <c r="M74">
-        <v>27.27396</v>
+        <v>27.652765</v>
       </c>
       <c r="N74">
-        <v>103.32604</v>
+        <v>102.947235</v>
       </c>
       <c r="O74">
-        <v>30.997812</v>
+        <v>30.8841705</v>
       </c>
       <c r="P74">
-        <v>72.328228</v>
+        <v>72.0630645</v>
       </c>
       <c r="Q74">
-        <v>84.228228</v>
+        <v>83.9630645</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2291792019717971</v>
+        <v>0.235243329021129</v>
       </c>
       <c r="T74">
-        <v>2.668390829451513</v>
+        <v>2.756631266933375</v>
       </c>
       <c r="U74">
         <v>0.0553</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.788450228716329</v>
+        <v>4.722855020103776</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.09177399883570482</v>
+        <v>0.09150662111930646</v>
       </c>
       <c r="C75">
-        <v>311.9270626187376</v>
+        <v>307.9300326330003</v>
       </c>
       <c r="D75">
-        <v>795.7770626187375</v>
+        <v>798.6300326330003</v>
       </c>
       <c r="E75">
-        <v>231.45</v>
+        <v>238.3</v>
       </c>
       <c r="F75">
-        <v>500.05</v>
+        <v>506.9</v>
       </c>
       <c r="G75">
         <v>16.2</v>
@@ -7437,28 +7437,28 @@
         <v>130.6</v>
       </c>
       <c r="M75">
-        <v>27.652765</v>
+        <v>28.03157</v>
       </c>
       <c r="N75">
-        <v>102.947235</v>
+        <v>102.56843</v>
       </c>
       <c r="O75">
-        <v>30.8841705</v>
+        <v>30.770529</v>
       </c>
       <c r="P75">
-        <v>72.0630645</v>
+        <v>71.797901</v>
       </c>
       <c r="Q75">
-        <v>83.9630645</v>
+        <v>83.697901</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.235243329021129</v>
+        <v>0.2417739273819479</v>
       </c>
       <c r="T75">
-        <v>2.756631266933375</v>
+        <v>2.851659430375381</v>
       </c>
       <c r="U75">
         <v>0.0553</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.722855020103776</v>
+        <v>4.659032654967239</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.09150662111930646</v>
+        <v>0.09123924340290812</v>
       </c>
       <c r="C76">
-        <v>307.9300326330003</v>
+        <v>303.9535328291003</v>
       </c>
       <c r="D76">
-        <v>798.6300326330003</v>
+        <v>801.5035328291002</v>
       </c>
       <c r="E76">
-        <v>238.3</v>
+        <v>245.15</v>
       </c>
       <c r="F76">
-        <v>506.9</v>
+        <v>513.75</v>
       </c>
       <c r="G76">
         <v>16.2</v>
@@ -7519,28 +7519,28 @@
         <v>130.6</v>
       </c>
       <c r="M76">
-        <v>28.03157</v>
+        <v>28.410375</v>
       </c>
       <c r="N76">
-        <v>102.56843</v>
+        <v>102.189625</v>
       </c>
       <c r="O76">
-        <v>30.770529</v>
+        <v>30.6568875</v>
       </c>
       <c r="P76">
-        <v>71.797901</v>
+        <v>71.5327375</v>
       </c>
       <c r="Q76">
-        <v>83.697901</v>
+        <v>83.4327375</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2417739273819479</v>
+        <v>0.2488269736116324</v>
       </c>
       <c r="T76">
-        <v>2.851659430375381</v>
+        <v>2.954289846892747</v>
       </c>
       <c r="U76">
         <v>0.0553</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>4.659032654967239</v>
+        <v>4.596912219567675</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.09123924340290812</v>
+        <v>0.09097186568650975</v>
       </c>
       <c r="C77">
-        <v>303.9535328291003</v>
+        <v>299.9977856123057</v>
       </c>
       <c r="D77">
-        <v>801.5035328291002</v>
+        <v>804.3977856123057</v>
       </c>
       <c r="E77">
-        <v>245.15</v>
+        <v>252</v>
       </c>
       <c r="F77">
-        <v>513.75</v>
+        <v>520.6</v>
       </c>
       <c r="G77">
         <v>16.2</v>
@@ -7601,28 +7601,28 @@
         <v>130.6</v>
       </c>
       <c r="M77">
-        <v>28.410375</v>
+        <v>28.78918</v>
       </c>
       <c r="N77">
-        <v>102.189625</v>
+        <v>101.81082</v>
       </c>
       <c r="O77">
-        <v>30.6568875</v>
+        <v>30.543246</v>
       </c>
       <c r="P77">
-        <v>71.5327375</v>
+        <v>71.267574</v>
       </c>
       <c r="Q77">
-        <v>83.4327375</v>
+        <v>83.167574</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2488269736116324</v>
+        <v>0.2564677736937906</v>
       </c>
       <c r="T77">
-        <v>2.954289846892747</v>
+        <v>3.065472798119893</v>
       </c>
       <c r="U77">
         <v>0.0553</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>4.596912219567675</v>
+        <v>4.5364265324681</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.09097186568650975</v>
+        <v>0.0920519879701114</v>
       </c>
       <c r="C78">
-        <v>299.9977856123057</v>
+        <v>281.582399815896</v>
       </c>
       <c r="D78">
-        <v>804.3977856123057</v>
+        <v>792.832399815896</v>
       </c>
       <c r="E78">
-        <v>252</v>
+        <v>258.85</v>
       </c>
       <c r="F78">
-        <v>520.6</v>
+        <v>527.45</v>
       </c>
       <c r="G78">
         <v>16.2</v>
@@ -7683,45 +7683,45 @@
         <v>130.6</v>
       </c>
       <c r="M78">
-        <v>28.78918</v>
+        <v>30.48661000000001</v>
       </c>
       <c r="N78">
-        <v>101.81082</v>
+        <v>100.11339</v>
       </c>
       <c r="O78">
-        <v>30.543246</v>
+        <v>30.03401699999999</v>
       </c>
       <c r="P78">
-        <v>71.267574</v>
+        <v>70.07937299999999</v>
       </c>
       <c r="Q78">
-        <v>83.167574</v>
+        <v>81.979373</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2564677736937906</v>
+        <v>0.2647729911743974</v>
       </c>
       <c r="T78">
-        <v>3.065472798119893</v>
+        <v>3.186323832062444</v>
       </c>
       <c r="U78">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V78">
         <v>0.3</v>
       </c>
       <c r="W78">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y78">
-        <v>4.5364265324681</v>
+        <v>4.283847892566604</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.0920519879701114</v>
+        <v>0.09180211025371304</v>
       </c>
       <c r="C79">
-        <v>281.582399815896</v>
+        <v>277.3782923035874</v>
       </c>
       <c r="D79">
-        <v>792.832399815896</v>
+        <v>795.4782923035874</v>
       </c>
       <c r="E79">
-        <v>258.85</v>
+        <v>265.7</v>
       </c>
       <c r="F79">
-        <v>527.45</v>
+        <v>534.3000000000001</v>
       </c>
       <c r="G79">
         <v>16.2</v>
@@ -7765,28 +7765,28 @@
         <v>130.6</v>
       </c>
       <c r="M79">
-        <v>30.48661000000001</v>
+        <v>30.88254000000001</v>
       </c>
       <c r="N79">
-        <v>100.11339</v>
+        <v>99.71745999999999</v>
       </c>
       <c r="O79">
-        <v>30.03401699999999</v>
+        <v>29.915238</v>
       </c>
       <c r="P79">
-        <v>70.07937299999999</v>
+        <v>69.802222</v>
       </c>
       <c r="Q79">
-        <v>81.979373</v>
+        <v>81.70222200000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2647729911743974</v>
+        <v>0.2738332284259684</v>
       </c>
       <c r="T79">
-        <v>3.186323832062444</v>
+        <v>3.318161323636135</v>
       </c>
       <c r="U79">
         <v>0.0578</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>4.283847892566604</v>
+        <v>4.228926765738827</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.09180211025371304</v>
+        <v>0.0915522325373147</v>
       </c>
       <c r="C80">
-        <v>277.3782923035874</v>
+        <v>273.1919040183005</v>
       </c>
       <c r="D80">
-        <v>795.4782923035874</v>
+        <v>798.1419040183005</v>
       </c>
       <c r="E80">
-        <v>265.7</v>
+        <v>272.55</v>
       </c>
       <c r="F80">
-        <v>534.3000000000001</v>
+        <v>541.15</v>
       </c>
       <c r="G80">
         <v>16.2</v>
@@ -7847,28 +7847,28 @@
         <v>130.6</v>
       </c>
       <c r="M80">
-        <v>30.88254000000001</v>
+        <v>31.27847</v>
       </c>
       <c r="N80">
-        <v>99.71745999999999</v>
+        <v>99.32153</v>
       </c>
       <c r="O80">
-        <v>29.915238</v>
+        <v>29.796459</v>
       </c>
       <c r="P80">
-        <v>69.802222</v>
+        <v>69.525071</v>
       </c>
       <c r="Q80">
-        <v>81.70222200000001</v>
+        <v>81.425071</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2738332284259684</v>
+        <v>0.2837563454157843</v>
       </c>
       <c r="T80">
-        <v>3.318161323636135</v>
+        <v>3.462554766788274</v>
       </c>
       <c r="U80">
         <v>0.0578</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>4.228926765738827</v>
+        <v>4.175396047185172</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.0915522325373147</v>
+        <v>0.09130235482091634</v>
       </c>
       <c r="C81">
-        <v>273.1919040183005</v>
+        <v>269.0234135533757</v>
       </c>
       <c r="D81">
-        <v>798.1419040183005</v>
+        <v>800.8234135533756</v>
       </c>
       <c r="E81">
-        <v>272.55</v>
+        <v>279.4</v>
       </c>
       <c r="F81">
-        <v>541.15</v>
+        <v>548</v>
       </c>
       <c r="G81">
         <v>16.2</v>
@@ -7929,28 +7929,28 @@
         <v>130.6</v>
       </c>
       <c r="M81">
-        <v>31.27847</v>
+        <v>31.6744</v>
       </c>
       <c r="N81">
-        <v>99.32153</v>
+        <v>98.92559999999999</v>
       </c>
       <c r="O81">
-        <v>29.796459</v>
+        <v>29.67768</v>
       </c>
       <c r="P81">
-        <v>69.525071</v>
+        <v>69.24791999999999</v>
       </c>
       <c r="Q81">
-        <v>81.425071</v>
+        <v>81.14792</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2837563454157843</v>
+        <v>0.2946717741045817</v>
       </c>
       <c r="T81">
-        <v>3.462554766788274</v>
+        <v>3.621387554255625</v>
       </c>
       <c r="U81">
         <v>0.0578</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>4.175396047185172</v>
+        <v>4.123203596595357</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.09130235482091634</v>
+        <v>0.091052477104518</v>
       </c>
       <c r="C82">
-        <v>269.0234135533757</v>
+        <v>264.8730019103167</v>
       </c>
       <c r="D82">
-        <v>800.8234135533756</v>
+        <v>803.5230019103167</v>
       </c>
       <c r="E82">
-        <v>279.4</v>
+        <v>286.25</v>
       </c>
       <c r="F82">
-        <v>548</v>
+        <v>554.85</v>
       </c>
       <c r="G82">
         <v>16.2</v>
@@ -8011,28 +8011,28 @@
         <v>130.6</v>
       </c>
       <c r="M82">
-        <v>31.6744</v>
+        <v>32.07033000000001</v>
       </c>
       <c r="N82">
-        <v>98.92559999999999</v>
+        <v>98.52966999999998</v>
       </c>
       <c r="O82">
-        <v>29.67768</v>
+        <v>29.55890099999999</v>
       </c>
       <c r="P82">
-        <v>69.24791999999999</v>
+        <v>68.97076899999999</v>
       </c>
       <c r="Q82">
-        <v>81.14792</v>
+        <v>80.870769</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2946717741045817</v>
+        <v>0.3067361952869369</v>
       </c>
       <c r="T82">
-        <v>3.621387554255625</v>
+        <v>3.796939582509015</v>
       </c>
       <c r="U82">
         <v>0.0578</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>4.123203596595357</v>
+        <v>4.072299848489241</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.091052477104518</v>
+        <v>0.09080259938811963</v>
       </c>
       <c r="C83">
-        <v>264.8730019103167</v>
+        <v>260.7408525395193</v>
       </c>
       <c r="D83">
-        <v>803.5230019103167</v>
+        <v>806.2408525395193</v>
       </c>
       <c r="E83">
-        <v>286.25</v>
+        <v>293.1</v>
       </c>
       <c r="F83">
-        <v>554.85</v>
+        <v>561.7</v>
       </c>
       <c r="G83">
         <v>16.2</v>
@@ -8093,28 +8093,28 @@
         <v>130.6</v>
       </c>
       <c r="M83">
-        <v>32.07033000000001</v>
+        <v>32.46626000000001</v>
       </c>
       <c r="N83">
-        <v>98.52966999999998</v>
+        <v>98.13373999999999</v>
       </c>
       <c r="O83">
-        <v>29.55890099999999</v>
+        <v>29.440122</v>
       </c>
       <c r="P83">
-        <v>68.97076899999999</v>
+        <v>68.69361799999999</v>
       </c>
       <c r="Q83">
-        <v>80.870769</v>
+        <v>80.59361799999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3067361952869369</v>
+        <v>0.3201411077117758</v>
       </c>
       <c r="T83">
-        <v>3.796939582509015</v>
+        <v>3.991997391679448</v>
       </c>
       <c r="U83">
         <v>0.0578</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>4.072299848489241</v>
+        <v>4.022637655214982</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.09080259938811963</v>
+        <v>0.09258622167172129</v>
       </c>
       <c r="C84">
-        <v>260.7408525395193</v>
+        <v>234.8841594117608</v>
       </c>
       <c r="D84">
-        <v>806.2408525395193</v>
+        <v>787.2341594117609</v>
       </c>
       <c r="E84">
-        <v>293.1</v>
+        <v>299.95</v>
       </c>
       <c r="F84">
-        <v>561.7</v>
+        <v>568.5500000000001</v>
       </c>
       <c r="G84">
         <v>16.2</v>
@@ -8175,45 +8175,45 @@
         <v>130.6</v>
       </c>
       <c r="M84">
-        <v>32.46626000000001</v>
+        <v>34.852115</v>
       </c>
       <c r="N84">
-        <v>98.13373999999999</v>
+        <v>95.747885</v>
       </c>
       <c r="O84">
-        <v>29.440122</v>
+        <v>28.7243655</v>
       </c>
       <c r="P84">
-        <v>68.69361799999999</v>
+        <v>67.02351949999999</v>
       </c>
       <c r="Q84">
-        <v>80.59361799999999</v>
+        <v>78.9235195</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3201411077117758</v>
+        <v>0.3351230686571841</v>
       </c>
       <c r="T84">
-        <v>3.991997391679448</v>
+        <v>4.210003178399343</v>
       </c>
       <c r="U84">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V84">
         <v>0.3</v>
       </c>
       <c r="W84">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y84">
-        <v>4.022637655214982</v>
+        <v>3.747261823278156</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.09258622167172129</v>
+        <v>0.09236084395532293</v>
       </c>
       <c r="C85">
-        <v>234.8841594117608</v>
+        <v>230.3862249038409</v>
       </c>
       <c r="D85">
-        <v>787.2341594117609</v>
+        <v>789.586224903841</v>
       </c>
       <c r="E85">
-        <v>299.95</v>
+        <v>306.8000000000001</v>
       </c>
       <c r="F85">
-        <v>568.5500000000001</v>
+        <v>575.4000000000001</v>
       </c>
       <c r="G85">
         <v>16.2</v>
@@ -8257,28 +8257,28 @@
         <v>130.6</v>
       </c>
       <c r="M85">
-        <v>34.852115</v>
+        <v>35.27202</v>
       </c>
       <c r="N85">
-        <v>95.747885</v>
+        <v>95.32798</v>
       </c>
       <c r="O85">
-        <v>28.7243655</v>
+        <v>28.598394</v>
       </c>
       <c r="P85">
-        <v>67.02351949999999</v>
+        <v>66.729586</v>
       </c>
       <c r="Q85">
-        <v>78.9235195</v>
+        <v>78.629586</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3351230686571841</v>
+        <v>0.3519777747207685</v>
       </c>
       <c r="T85">
-        <v>4.210003178399343</v>
+        <v>4.455259688459225</v>
       </c>
       <c r="U85">
         <v>0.0613</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.747261823278156</v>
+        <v>3.702651563477226</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.09236084395532293</v>
+        <v>0.09213546623892457</v>
       </c>
       <c r="C86">
-        <v>230.386224903841</v>
+        <v>225.9023873211073</v>
       </c>
       <c r="D86">
-        <v>789.586224903841</v>
+        <v>791.9523873211073</v>
       </c>
       <c r="E86">
-        <v>306.8</v>
+        <v>313.65</v>
       </c>
       <c r="F86">
-        <v>575.4</v>
+        <v>582.25</v>
       </c>
       <c r="G86">
         <v>16.2</v>
@@ -8339,28 +8339,28 @@
         <v>130.6</v>
       </c>
       <c r="M86">
-        <v>35.27202</v>
+        <v>35.691925</v>
       </c>
       <c r="N86">
-        <v>95.32798</v>
+        <v>94.908075</v>
       </c>
       <c r="O86">
-        <v>28.598394</v>
+        <v>28.4724225</v>
       </c>
       <c r="P86">
-        <v>66.729586</v>
+        <v>66.4356525</v>
       </c>
       <c r="Q86">
-        <v>78.629586</v>
+        <v>78.33565250000001</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3519777747207682</v>
+        <v>0.3710797749261638</v>
       </c>
       <c r="T86">
-        <v>4.455259688459222</v>
+        <v>4.733217066527089</v>
       </c>
       <c r="U86">
         <v>0.0613</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.702651563477227</v>
+        <v>3.659090956848082</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.09213546623892457</v>
+        <v>0.0919100885225262</v>
       </c>
       <c r="C87">
-        <v>225.9023873211073</v>
+        <v>221.4327737777543</v>
       </c>
       <c r="D87">
-        <v>791.9523873211073</v>
+        <v>794.3327737777543</v>
       </c>
       <c r="E87">
-        <v>313.65</v>
+        <v>320.5</v>
       </c>
       <c r="F87">
-        <v>582.25</v>
+        <v>589.1</v>
       </c>
       <c r="G87">
         <v>16.2</v>
@@ -8421,28 +8421,28 @@
         <v>130.6</v>
       </c>
       <c r="M87">
-        <v>35.691925</v>
+        <v>36.11183</v>
       </c>
       <c r="N87">
-        <v>94.908075</v>
+        <v>94.48817</v>
       </c>
       <c r="O87">
-        <v>28.4724225</v>
+        <v>28.346451</v>
       </c>
       <c r="P87">
-        <v>66.4356525</v>
+        <v>66.14171899999999</v>
       </c>
       <c r="Q87">
-        <v>78.33565250000001</v>
+        <v>78.041719</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3710797749261638</v>
+        <v>0.3929106323037586</v>
       </c>
       <c r="T87">
-        <v>4.733217066527089</v>
+        <v>5.050882641461792</v>
       </c>
       <c r="U87">
         <v>0.0613</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.659090956848082</v>
+        <v>3.616543387582407</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.0919100885225262</v>
+        <v>0.09168471080612786</v>
       </c>
       <c r="C88">
-        <v>221.4327737777543</v>
+        <v>216.9775129208607</v>
       </c>
       <c r="D88">
-        <v>794.3327737777543</v>
+        <v>796.7275129208607</v>
       </c>
       <c r="E88">
-        <v>320.5</v>
+        <v>327.35</v>
       </c>
       <c r="F88">
-        <v>589.1</v>
+        <v>595.95</v>
       </c>
       <c r="G88">
         <v>16.2</v>
@@ -8503,28 +8503,28 @@
         <v>130.6</v>
       </c>
       <c r="M88">
-        <v>36.11183</v>
+        <v>36.531735</v>
       </c>
       <c r="N88">
-        <v>94.48817</v>
+        <v>94.068265</v>
       </c>
       <c r="O88">
-        <v>28.346451</v>
+        <v>28.2204795</v>
       </c>
       <c r="P88">
-        <v>66.14171899999999</v>
+        <v>65.8477855</v>
       </c>
       <c r="Q88">
-        <v>78.041719</v>
+        <v>77.74778550000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3929106323037586</v>
+        <v>0.4181000831240604</v>
       </c>
       <c r="T88">
-        <v>5.050882641461792</v>
+        <v>5.417419843309528</v>
       </c>
       <c r="U88">
         <v>0.0613</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.616543387582407</v>
+        <v>3.574973923357322</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.09168471080612786</v>
+        <v>0.09145933308972951</v>
       </c>
       <c r="C89">
-        <v>216.9775129208607</v>
+        <v>212.5367349535693</v>
       </c>
       <c r="D89">
-        <v>796.7275129208607</v>
+        <v>799.1367349535692</v>
       </c>
       <c r="E89">
-        <v>327.35</v>
+        <v>334.1999999999999</v>
       </c>
       <c r="F89">
-        <v>595.95</v>
+        <v>602.8</v>
       </c>
       <c r="G89">
         <v>16.2</v>
@@ -8585,28 +8585,28 @@
         <v>130.6</v>
       </c>
       <c r="M89">
-        <v>36.531735</v>
+        <v>36.95164</v>
       </c>
       <c r="N89">
-        <v>94.068265</v>
+        <v>93.64836</v>
       </c>
       <c r="O89">
-        <v>28.2204795</v>
+        <v>28.094508</v>
       </c>
       <c r="P89">
-        <v>65.8477855</v>
+        <v>65.55385200000001</v>
       </c>
       <c r="Q89">
-        <v>77.74778550000001</v>
+        <v>77.45385200000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4181000831240604</v>
+        <v>0.447487775747746</v>
       </c>
       <c r="T89">
-        <v>5.417419843309528</v>
+        <v>5.845046578798553</v>
       </c>
       <c r="U89">
         <v>0.0613</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.574973923357322</v>
+        <v>3.534349219682807</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.09145933308972951</v>
+        <v>0.09297835537333116</v>
       </c>
       <c r="C90">
-        <v>212.5367349535693</v>
+        <v>189.7250395131307</v>
       </c>
       <c r="D90">
-        <v>799.1367349535692</v>
+        <v>783.1750395131306</v>
       </c>
       <c r="E90">
-        <v>334.1999999999999</v>
+        <v>341.05</v>
       </c>
       <c r="F90">
-        <v>602.8</v>
+        <v>609.65</v>
       </c>
       <c r="G90">
         <v>16.2</v>
@@ -8667,45 +8667,45 @@
         <v>130.6</v>
       </c>
       <c r="M90">
-        <v>36.95164</v>
+        <v>39.078565</v>
       </c>
       <c r="N90">
-        <v>93.64836</v>
+        <v>91.521435</v>
       </c>
       <c r="O90">
-        <v>28.094508</v>
+        <v>27.4564305</v>
       </c>
       <c r="P90">
-        <v>65.55385200000001</v>
+        <v>64.0650045</v>
       </c>
       <c r="Q90">
-        <v>77.45385200000001</v>
+        <v>75.96500450000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.447487775747746</v>
+        <v>0.4822186852121015</v>
       </c>
       <c r="T90">
-        <v>5.845046578798553</v>
+        <v>6.350423629831037</v>
       </c>
       <c r="U90">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V90">
         <v>0.3</v>
       </c>
       <c r="W90">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y90">
-        <v>3.534349219682807</v>
+        <v>3.341985561649974</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.09297835537333116</v>
+        <v>0.09277257765693279</v>
       </c>
       <c r="C91">
-        <v>189.7250395131307</v>
+        <v>184.9998864844092</v>
       </c>
       <c r="D91">
-        <v>783.1750395131306</v>
+        <v>785.2998864844092</v>
       </c>
       <c r="E91">
-        <v>341.05</v>
+        <v>347.9</v>
       </c>
       <c r="F91">
-        <v>609.65</v>
+        <v>616.5</v>
       </c>
       <c r="G91">
         <v>16.2</v>
@@ -8749,28 +8749,28 @@
         <v>130.6</v>
       </c>
       <c r="M91">
-        <v>39.078565</v>
+        <v>39.51765</v>
       </c>
       <c r="N91">
-        <v>91.521435</v>
+        <v>91.08234999999999</v>
       </c>
       <c r="O91">
-        <v>27.4564305</v>
+        <v>27.324705</v>
       </c>
       <c r="P91">
-        <v>64.0650045</v>
+        <v>63.757645</v>
       </c>
       <c r="Q91">
-        <v>75.96500450000001</v>
+        <v>75.657645</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4822186852121015</v>
+        <v>0.5238957765693281</v>
       </c>
       <c r="T91">
-        <v>6.350423629831037</v>
+        <v>6.956876091070018</v>
       </c>
       <c r="U91">
         <v>0.0641</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>3.341985561649974</v>
+        <v>3.304852388742751</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.09277257765693279</v>
+        <v>0.09256679994053443</v>
       </c>
       <c r="C92">
-        <v>184.9998864844092</v>
+        <v>180.2862947476368</v>
       </c>
       <c r="D92">
-        <v>785.2998864844092</v>
+        <v>787.4362947476368</v>
       </c>
       <c r="E92">
-        <v>347.9</v>
+        <v>354.75</v>
       </c>
       <c r="F92">
-        <v>616.5</v>
+        <v>623.35</v>
       </c>
       <c r="G92">
         <v>16.2</v>
@@ -8831,28 +8831,28 @@
         <v>130.6</v>
       </c>
       <c r="M92">
-        <v>39.51765</v>
+        <v>39.956735</v>
       </c>
       <c r="N92">
-        <v>91.08234999999999</v>
+        <v>90.64326499999999</v>
       </c>
       <c r="O92">
-        <v>27.324705</v>
+        <v>27.1929795</v>
       </c>
       <c r="P92">
-        <v>63.757645</v>
+        <v>63.45028549999999</v>
       </c>
       <c r="Q92">
-        <v>75.657645</v>
+        <v>75.3502855</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5238957765693281</v>
+        <v>0.5748344437837162</v>
       </c>
       <c r="T92">
-        <v>6.956876091070018</v>
+        <v>7.698095765917661</v>
       </c>
       <c r="U92">
         <v>0.0641</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>3.304852388742751</v>
+        <v>3.268535329525798</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.09256679994053443</v>
+        <v>0.09236102222413609</v>
       </c>
       <c r="C93">
-        <v>180.2862947476368</v>
+        <v>175.5843589176935</v>
       </c>
       <c r="D93">
-        <v>787.4362947476368</v>
+        <v>789.5843589176935</v>
       </c>
       <c r="E93">
-        <v>354.75</v>
+        <v>361.6</v>
       </c>
       <c r="F93">
-        <v>623.35</v>
+        <v>630.2</v>
       </c>
       <c r="G93">
         <v>16.2</v>
@@ -8913,28 +8913,28 @@
         <v>130.6</v>
       </c>
       <c r="M93">
-        <v>39.956735</v>
+        <v>40.39582000000001</v>
       </c>
       <c r="N93">
-        <v>90.64326499999999</v>
+        <v>90.20417999999998</v>
       </c>
       <c r="O93">
-        <v>27.1929795</v>
+        <v>27.06125399999999</v>
       </c>
       <c r="P93">
-        <v>63.45028549999999</v>
+        <v>63.14292599999999</v>
       </c>
       <c r="Q93">
-        <v>75.3502855</v>
+        <v>75.04292599999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5748344437837162</v>
+        <v>0.6385077778017014</v>
       </c>
       <c r="T93">
-        <v>7.698095765917661</v>
+        <v>8.624620359477216</v>
       </c>
       <c r="U93">
         <v>0.0641</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>3.268535329525798</v>
+        <v>3.233007771596169</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.09236102222413609</v>
+        <v>0.09215524450773774</v>
       </c>
       <c r="C94">
-        <v>175.5843589176935</v>
+        <v>170.894174644692</v>
       </c>
       <c r="D94">
-        <v>789.5843589176935</v>
+        <v>791.7441746446921</v>
       </c>
       <c r="E94">
-        <v>361.6</v>
+        <v>368.45</v>
       </c>
       <c r="F94">
-        <v>630.2</v>
+        <v>637.0500000000001</v>
       </c>
       <c r="G94">
         <v>16.2</v>
@@ -8995,28 +8995,28 @@
         <v>130.6</v>
       </c>
       <c r="M94">
-        <v>40.39582000000001</v>
+        <v>40.83490500000001</v>
       </c>
       <c r="N94">
-        <v>90.20417999999998</v>
+        <v>89.76509499999999</v>
       </c>
       <c r="O94">
-        <v>27.06125399999999</v>
+        <v>26.9295285</v>
       </c>
       <c r="P94">
-        <v>63.14292599999999</v>
+        <v>62.83556649999999</v>
       </c>
       <c r="Q94">
-        <v>75.04292599999999</v>
+        <v>74.7355665</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6385077778017014</v>
+        <v>0.7203734929676823</v>
       </c>
       <c r="T94">
-        <v>8.624620359477216</v>
+        <v>9.815866265482358</v>
       </c>
       <c r="U94">
         <v>0.0641</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>3.233007771596169</v>
+        <v>3.198244247170404</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.09215524450773774</v>
+        <v>0.09194946679133938</v>
       </c>
       <c r="C95">
-        <v>170.894174644692</v>
+        <v>166.2158386281743</v>
       </c>
       <c r="D95">
-        <v>791.7441746446921</v>
+        <v>793.9158386281744</v>
       </c>
       <c r="E95">
-        <v>368.45</v>
+        <v>375.3000000000001</v>
       </c>
       <c r="F95">
-        <v>637.0500000000001</v>
+        <v>643.9000000000001</v>
       </c>
       <c r="G95">
         <v>16.2</v>
@@ -9077,28 +9077,28 @@
         <v>130.6</v>
       </c>
       <c r="M95">
-        <v>40.83490500000001</v>
+        <v>41.27399000000001</v>
       </c>
       <c r="N95">
-        <v>89.76509499999999</v>
+        <v>89.32600999999998</v>
       </c>
       <c r="O95">
-        <v>26.9295285</v>
+        <v>26.79780299999999</v>
       </c>
       <c r="P95">
-        <v>62.83556649999999</v>
+        <v>62.52820699999999</v>
       </c>
       <c r="Q95">
-        <v>74.7355665</v>
+        <v>74.42820699999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7203734929676823</v>
+        <v>0.8295277798556571</v>
       </c>
       <c r="T95">
-        <v>9.815866265482358</v>
+        <v>11.40419414015588</v>
       </c>
       <c r="U95">
         <v>0.0641</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>3.198244247170404</v>
+        <v>3.164220372200506</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.09194946679133938</v>
+        <v>0.09174368907494103</v>
       </c>
       <c r="C96">
-        <v>166.2158386281743</v>
+        <v>161.5494486315432</v>
       </c>
       <c r="D96">
-        <v>793.9158386281744</v>
+        <v>796.0994486315432</v>
       </c>
       <c r="E96">
-        <v>375.3000000000001</v>
+        <v>382.15</v>
       </c>
       <c r="F96">
-        <v>643.9000000000001</v>
+        <v>650.75</v>
       </c>
       <c r="G96">
         <v>16.2</v>
@@ -9159,28 +9159,28 @@
         <v>130.6</v>
       </c>
       <c r="M96">
-        <v>41.27399000000001</v>
+        <v>41.713075</v>
       </c>
       <c r="N96">
-        <v>89.32600999999998</v>
+        <v>88.88692499999999</v>
       </c>
       <c r="O96">
-        <v>26.79780299999999</v>
+        <v>26.6660775</v>
       </c>
       <c r="P96">
-        <v>62.52820699999999</v>
+        <v>62.22084749999999</v>
       </c>
       <c r="Q96">
-        <v>74.42820699999999</v>
+        <v>74.1208475</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8295277798556571</v>
+        <v>0.9823437814988218</v>
       </c>
       <c r="T96">
-        <v>11.40419414015588</v>
+        <v>13.62785316469882</v>
       </c>
       <c r="U96">
         <v>0.0641</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>3.164220372200506</v>
+        <v>3.130912789335238</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.09174368907494103</v>
+        <v>0.09153791135854268</v>
       </c>
       <c r="C97">
-        <v>161.5494486315432</v>
+        <v>156.8951034967337</v>
       </c>
       <c r="D97">
-        <v>796.0994486315432</v>
+        <v>798.2951034967336</v>
       </c>
       <c r="E97">
-        <v>382.15</v>
+        <v>389</v>
       </c>
       <c r="F97">
-        <v>650.75</v>
+        <v>657.6</v>
       </c>
       <c r="G97">
         <v>16.2</v>
@@ -9241,28 +9241,28 @@
         <v>130.6</v>
       </c>
       <c r="M97">
-        <v>41.713075</v>
+        <v>42.15216</v>
       </c>
       <c r="N97">
-        <v>88.88692499999999</v>
+        <v>88.44783999999999</v>
       </c>
       <c r="O97">
-        <v>26.6660775</v>
+        <v>26.53435199999999</v>
       </c>
       <c r="P97">
-        <v>62.22084749999999</v>
+        <v>61.91348799999999</v>
       </c>
       <c r="Q97">
-        <v>74.1208475</v>
+        <v>73.81348799999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9823437814988218</v>
+        <v>1.211567783963569</v>
       </c>
       <c r="T97">
-        <v>13.62785316469882</v>
+        <v>16.96334170151322</v>
       </c>
       <c r="U97">
         <v>0.0641</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>3.130912789335238</v>
+        <v>3.098299114446329</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.09153791135854268</v>
+        <v>0.09133213364214432</v>
       </c>
       <c r="C98">
-        <v>156.8951034967337</v>
+        <v>152.2529031591278</v>
       </c>
       <c r="D98">
-        <v>798.2951034967336</v>
+        <v>800.5029031591276</v>
       </c>
       <c r="E98">
-        <v>389</v>
+        <v>395.8499999999999</v>
       </c>
       <c r="F98">
-        <v>657.6</v>
+        <v>664.4499999999999</v>
       </c>
       <c r="G98">
         <v>16.2</v>
@@ -9323,28 +9323,28 @@
         <v>130.6</v>
       </c>
       <c r="M98">
-        <v>42.15216</v>
+        <v>42.591245</v>
       </c>
       <c r="N98">
-        <v>88.44783999999999</v>
+        <v>88.00875499999999</v>
       </c>
       <c r="O98">
-        <v>26.53435199999999</v>
+        <v>26.4026265</v>
       </c>
       <c r="P98">
-        <v>61.91348799999999</v>
+        <v>61.6061285</v>
       </c>
       <c r="Q98">
-        <v>73.81348799999999</v>
+        <v>73.5061285</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.211567783963566</v>
+        <v>1.593607788071476</v>
       </c>
       <c r="T98">
-        <v>16.96334170151318</v>
+        <v>22.52248926287049</v>
       </c>
       <c r="U98">
         <v>0.0641</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>3.098299114446329</v>
+        <v>3.066357886462347</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.09133213364214432</v>
+        <v>0.09112635592574597</v>
       </c>
       <c r="C99">
-        <v>152.2529031591278</v>
+        <v>147.6229486627144</v>
       </c>
       <c r="D99">
-        <v>800.5029031591276</v>
+        <v>802.7229486627143</v>
       </c>
       <c r="E99">
-        <v>395.8499999999999</v>
+        <v>402.6999999999999</v>
       </c>
       <c r="F99">
-        <v>664.4499999999999</v>
+        <v>671.3</v>
       </c>
       <c r="G99">
         <v>16.2</v>
@@ -9405,28 +9405,28 @@
         <v>130.6</v>
       </c>
       <c r="M99">
-        <v>42.591245</v>
+        <v>43.03033</v>
       </c>
       <c r="N99">
-        <v>88.00875499999999</v>
+        <v>87.56967</v>
       </c>
       <c r="O99">
-        <v>26.4026265</v>
+        <v>26.270901</v>
       </c>
       <c r="P99">
-        <v>61.6061285</v>
+        <v>61.29876900000001</v>
       </c>
       <c r="Q99">
-        <v>73.5061285</v>
+        <v>73.19876900000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.593607788071476</v>
+        <v>2.357687796287296</v>
       </c>
       <c r="T99">
-        <v>22.52248926287049</v>
+        <v>33.64078438558512</v>
       </c>
       <c r="U99">
         <v>0.0641</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>3.066357886462347</v>
+        <v>3.035068520273956</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.09112635592574597</v>
+        <v>0.09092057820934761</v>
       </c>
       <c r="C100">
-        <v>147.6229486627144</v>
+        <v>143.0053421755081</v>
       </c>
       <c r="D100">
-        <v>802.7229486627143</v>
+        <v>804.955342175508</v>
       </c>
       <c r="E100">
-        <v>402.6999999999999</v>
+        <v>409.55</v>
       </c>
       <c r="F100">
-        <v>671.3</v>
+        <v>678.15</v>
       </c>
       <c r="G100">
         <v>16.2</v>
@@ -9487,28 +9487,28 @@
         <v>130.6</v>
       </c>
       <c r="M100">
-        <v>43.03033</v>
+        <v>43.469415</v>
       </c>
       <c r="N100">
-        <v>87.56967</v>
+        <v>87.130585</v>
       </c>
       <c r="O100">
-        <v>26.270901</v>
+        <v>26.1391755</v>
       </c>
       <c r="P100">
-        <v>61.29876900000001</v>
+        <v>60.9914095</v>
       </c>
       <c r="Q100">
-        <v>73.19876900000001</v>
+        <v>72.89140950000001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.357687796287296</v>
+        <v>4.649927820934757</v>
       </c>
       <c r="T100">
-        <v>33.64078438558512</v>
+        <v>66.995669753729</v>
       </c>
       <c r="U100">
         <v>0.0641</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>3.035068520273956</v>
+        <v>3.004411262493411</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.09092057820934761</v>
-      </c>
-      <c r="C101">
-        <v>143.0053421755081</v>
-      </c>
-      <c r="D101">
-        <v>804.955342175508</v>
-      </c>
-      <c r="E101">
-        <v>409.55</v>
-      </c>
-      <c r="F101">
-        <v>678.15</v>
-      </c>
-      <c r="G101">
-        <v>16.2</v>
-      </c>
-      <c r="H101">
-        <v>416.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>142.5</v>
-      </c>
-      <c r="K101">
-        <v>11.90000000000001</v>
-      </c>
-      <c r="L101">
-        <v>130.6</v>
-      </c>
-      <c r="M101">
-        <v>43.469415</v>
-      </c>
-      <c r="N101">
-        <v>87.130585</v>
-      </c>
-      <c r="O101">
-        <v>26.1391755</v>
-      </c>
-      <c r="P101">
-        <v>60.9914095</v>
-      </c>
-      <c r="Q101">
-        <v>72.89140950000001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.649927820934757</v>
-      </c>
-      <c r="T101">
-        <v>66.995669753729</v>
-      </c>
-      <c r="U101">
-        <v>0.0641</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.04487</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>Ba2/BB</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>3.004411262493411</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
